--- a/EXCEL/M02/bus123-excel-m02-l01-starter.xlsx
+++ b/EXCEL/M02/bus123-excel-m02-l01-starter.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R6f3a197d7572436e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="Raea61ff5d9074b79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Export" sheetId="3" r:id="Rc3c802e31e784408"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manager View" sheetId="4" r:id="Rd15124fb8b3f47e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="5" r:id="Rc97c2996f8f64115"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="6" r:id="R2527ebf4b5bc48c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R8b6792c39a07466a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R426c2f86b4ec451f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Export" sheetId="3" r:id="Rcdd3080958da45df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manager View" sheetId="4" r:id="R5b721644b4ff405f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="5" r:id="R667e9741eef24096"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="6" r:id="R605b5a3efd014808"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,10 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="200" formatCode="$#,##0"/>
+    <x:numFmt numFmtId="201" formatCode="General"/>
   </x:numFmts>
-  <x:fonts count="11">
+  <x:fonts count="20">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -84,8 +85,61 @@
       <x:color rgb="FF355773"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="15"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos Display"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF1A1F2C"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="15"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1A1F2C"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF4A7C5E"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1A1F2C"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF355773"/>
+      <x:name val="Aptos Mono"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="19">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -132,8 +186,53 @@
         <x:fgColor rgb="FFE5E7EB"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0E1116"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF355773"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4A7C5E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFAF8F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE9EDF2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF1C7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7E7E0"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="19">
+  <x:borders count="35">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -315,11 +414,139 @@
         <x:color rgb="FFD1D5DB"/>
       </x:top>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DCE3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9B44A"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD9B44A"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD9B44A"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9B44A"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9B44A"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9B44A"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9B44A"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9B44A"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9B44A"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9B44A"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="95">
+  <x:cellXfs count="191">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -502,6 +729,214 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="12" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="15" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="15" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="12" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="12" fillId="12" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="12" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="12" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="12" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="16" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="16" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -705,138 +1140,138 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="32" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="29" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="29" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="29" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="96" t="str">
         <x:v>BUS123 · EXCEL-M02-L01 · Formatting and Organizing Worksheets</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
+      <x:c r="B1" s="96"/>
+      <x:c r="C1" s="96"/>
+      <x:c r="D1" s="96"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="7" t="str">
-        <x:v>Anchor &amp; Oak Events · Raw export to manager-ready workbook</x:v>
-      </x:c>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="12" t="str">
-        <x:v>The Scenario</x:v>
-      </x:c>
-      <x:c r="B4" s="12" t="str">
-        <x:v>Start in Class</x:v>
-      </x:c>
-      <x:c r="C4" s="12" t="str">
-        <x:v>Finish for Homework</x:v>
-      </x:c>
-      <x:c r="D4" s="12" t="str">
-        <x:v>Submit</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="105" customHeight="1">
-      <x:c r="A5" s="15" t="str">
-        <x:v>Anchor &amp; Oak exported 24 event records. Preserve the Raw Export exactly, then turn the separate Manager View copy into a trustworthy workbook a manager can scan, filter, and use.</x:v>
-      </x:c>
-      <x:c r="B5" s="15" t="str">
-        <x:v>Complete Live You Try It. Then build the Manager View structure: table, filters, number formats, alignment, column widths, and Freeze Panes. Plan for about 25 minutes.</x:v>
-      </x:c>
-      <x:c r="C5" s="15" t="str">
-        <x:v>Add four summary formulas, purposeful conditional formatting, and a final 30-second audit. Plan for about 30–40 minutes after class.</x:v>
-      </x:c>
-      <x:c r="D5" s="15" t="str">
-        <x:v>Upload the original .xlsx. Keep the required worksheet names. Do not delete, rename, reorder, or edit Raw Export.</x:v>
+      <x:c r="A2" s="97" t="str">
+        <x:v>Anchor &amp; Oak Events · One source, one working view, one manager-ready handoff</x:v>
+      </x:c>
+      <x:c r="B2" s="97"/>
+      <x:c r="C2" s="97"/>
+      <x:c r="D2" s="97"/>
+    </x:row>
+    <x:row r="4" ht="25" customHeight="1">
+      <x:c r="A4" s="98" t="str">
+        <x:v>Before Class</x:v>
+      </x:c>
+      <x:c r="B4" s="98" t="str">
+        <x:v>Guided Practice</x:v>
+      </x:c>
+      <x:c r="C4" s="98" t="str">
+        <x:v>Class Challenge</x:v>
+      </x:c>
+      <x:c r="D4" s="98" t="str">
+        <x:v>Finish + Submit</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="95" customHeight="1">
+      <x:c r="A5" s="101" t="str">
+        <x:v>Read the pre-reading. Open this workbook only to observe the tabs. Do not edit Raw Export or begin Manager View yet.</x:v>
+      </x:c>
+      <x:c r="B5" s="101" t="str">
+        <x:v>Complete the two Live You Try It formatting checkpoints when the slides direct you. The supplied data is already entered; focus on formatting decisions.</x:v>
+      </x:c>
+      <x:c r="C5" s="101" t="str">
+        <x:v>When directed, preserve Raw Export and spend about 25 minutes building the Manager View structure: table, filters, formats, widths, alignment, and Freeze Panes.</x:v>
+      </x:c>
+      <x:c r="D5" s="101" t="str">
+        <x:v>Finish four summary formulas, one purposeful conditional-formatting rule, and the 30-second audit. Upload the completed original .xlsx.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="17" t="str">
+      <x:c r="A8" s="104" t="str">
         <x:v>Learning objectives</x:v>
       </x:c>
-      <x:c r="B8" s="17"/>
-      <x:c r="C8" s="17"/>
-      <x:c r="D8" s="17"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="33" t="str">
+      <x:c r="B8" s="104"/>
+      <x:c r="C8" s="104"/>
+      <x:c r="D8" s="104"/>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="105" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B9" s="25" t="str">
+      <x:c r="B9" s="108" t="str">
         <x:v>Preserve source data while creating a separate working view.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="34" t="str">
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="106" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B10" s="27" t="str">
+      <x:c r="B10" s="109" t="str">
         <x:v>Apply meaningful date, whole-number, and business currency formats.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="34" t="str">
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="106" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B11" s="27" t="str">
+      <x:c r="B11" s="109" t="str">
         <x:v>Use tables, filters, Freeze Panes, alignment, and readable widths to support scanning.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="34" t="str">
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="106" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B12" s="27" t="str">
-        <x:v>Build auditable summary formulas using worksheet references.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="34" t="str">
+      <x:c r="B12" s="109" t="str">
+        <x:v>Build auditable summary formulas with worksheet or table references.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="106" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B13" s="27" t="str">
+      <x:c r="B13" s="109" t="str">
         <x:v>Apply conditional formatting for a named business purpose.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="35" t="str">
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="107" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B14" s="29" t="str">
+      <x:c r="B14" s="110" t="str">
         <x:v>Use visual hierarchy without relying on one prescribed palette or layout style.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="41" t="str">
+      <x:c r="A17" s="111" t="str">
         <x:v>Grading</x:v>
       </x:c>
-      <x:c r="B17" s="41" t="str">
+      <x:c r="B17" s="111" t="str">
         <x:v>Automatically checked</x:v>
       </x:c>
-      <x:c r="C17" s="41" t="str">
+      <x:c r="C17" s="111" t="str">
         <x:v>Flagged spot-check</x:v>
       </x:c>
-      <x:c r="D17" s="41" t="str">
+      <x:c r="D17" s="111" t="str">
         <x:v>Important boundary</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="95" customHeight="1">
-      <x:c r="A18" s="15" t="str">
+    <x:row r="18" ht="78" customHeight="1">
+      <x:c r="A18" s="101" t="str">
         <x:v>30 points total</x:v>
       </x:c>
-      <x:c r="B18" s="15" t="str">
-        <x:v>27 points (90%): structure, source integrity, table/filters, Freeze Panes, number formats, formulas, conditional formatting, and minimum widths.</x:v>
-      </x:c>
-      <x:c r="C18" s="15" t="str">
-        <x:v>3 points (10%): visual hierarchy, alignment, and whether color choices have a clear business purpose.</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="str">
-        <x:v>Live You Try It is self-checking practice only. The Class Challenge is the only graded activity.</x:v>
+      <x:c r="B18" s="101" t="str">
+        <x:v>27 points: source integrity, table/filters, Freeze Panes, number formats, formulas, conditional formatting, and minimum widths.</x:v>
+      </x:c>
+      <x:c r="C18" s="101" t="str">
+        <x:v>3 points: visual hierarchy, alignment, and whether color choices have a clear business purpose.</x:v>
+      </x:c>
+      <x:c r="D18" s="101" t="str">
+        <x:v>Live You Try It is ungraded practice. The completed Manager View is the only graded activity. Never edit Raw Export.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -853,257 +1288,335 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="27" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
-        <x:v>Live You Try It</x:v>
-      </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="7" t="str">
-        <x:v>Low-stakes, self-checking practice. Enter the slide givens in yellow cells, then build formulas with cell references. This sheet is not graded.</x:v>
-      </x:c>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="17" t="str">
-        <x:v>Pause 1 · Spring Gala net profit</x:v>
-      </x:c>
-      <x:c r="B5" s="17"/>
-      <x:c r="C5" s="17"/>
-      <x:c r="D5" s="17"/>
-      <x:c r="E5" s="17"/>
+      <x:c r="A1" s="114" t="str">
+        <x:v>Live You Try It · Formatting Practice</x:v>
+      </x:c>
+      <x:c r="B1" s="114"/>
+      <x:c r="C1" s="114"/>
+      <x:c r="D1" s="114"/>
+      <x:c r="E1" s="114"/>
+    </x:row>
+    <x:row r="2" ht="34" customHeight="1">
+      <x:c r="A2" s="117" t="str">
+        <x:v>The event data is already entered. Make formatting decisions instead of retyping slide values. This sheet is not graded.</x:v>
+      </x:c>
+      <x:c r="B2" s="117"/>
+      <x:c r="C2" s="117"/>
+      <x:c r="D2" s="117"/>
+      <x:c r="E2" s="117"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="104" t="str">
+        <x:v>Checkpoint 1 · 6 minutes · Make the supplied records readable</x:v>
+      </x:c>
+      <x:c r="B4" s="104"/>
+      <x:c r="C4" s="104"/>
+      <x:c r="D4" s="104"/>
+      <x:c r="E4" s="104"/>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="127" t="str">
+        <x:v>WHAT + HOW · Format Event Date as a readable date, Guests as a whole number, and Revenue / Net Profit as business money. Then make the headers and widths easy to scan.</x:v>
+      </x:c>
+      <x:c r="B5" s="128"/>
+      <x:c r="C5" s="128"/>
+      <x:c r="D5" s="128"/>
+      <x:c r="E5" s="129"/>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="130" t="str">
+        <x:v>DELIVERABLE · A six-row practice table whose dates, counts, money, labels, and alignment communicate clearly without changing any value.</x:v>
+      </x:c>
+      <x:c r="B6" s="131"/>
+      <x:c r="C6" s="131"/>
+      <x:c r="D6" s="131"/>
+      <x:c r="E6" s="132"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="41" t="str">
-        <x:v>Step</x:v>
-      </x:c>
-      <x:c r="B7" s="41" t="str">
-        <x:v>Your Cell</x:v>
-      </x:c>
-      <x:c r="C7" s="41" t="str">
-        <x:v>Hint / Check</x:v>
-      </x:c>
-      <x:c r="D7" s="41" t="str">
-        <x:v>Feedback</x:v>
-      </x:c>
-      <x:c r="E7" s="41" t="str">
-        <x:v>Practice Status</x:v>
+      <x:c r="A7" s="136" t="str">
+        <x:v>Event</x:v>
+      </x:c>
+      <x:c r="B7" s="136" t="str">
+        <x:v>Event Date</x:v>
+      </x:c>
+      <x:c r="C7" s="136" t="str">
+        <x:v>Guests</x:v>
+      </x:c>
+      <x:c r="D7" s="136" t="str">
+        <x:v>Revenue</x:v>
+      </x:c>
+      <x:c r="E7" s="136" t="str">
+        <x:v>Net Profit</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="str">
-        <x:v>Revenue</x:v>
-      </x:c>
-      <x:c r="B8" s="48"/>
-      <x:c r="C8" t="str">
-        <x:v>Type the slide given first</x:v>
+      <x:c r="A8" s="139" t="str">
+        <x:v>Spring Gala</x:v>
+      </x:c>
+      <x:c r="B8" s="140" t="n">
+        <x:v>46096</x:v>
+      </x:c>
+      <x:c r="C8" s="140" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D8" s="140" t="n">
+        <x:v>4800</x:v>
+      </x:c>
+      <x:c r="E8" s="140" t="n">
+        <x:v>2980</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>Catering</x:v>
-      </x:c>
-      <x:c r="B9" s="48"/>
-      <x:c r="C9" t="str">
-        <x:v>Type the slide given first</x:v>
+      <x:c r="A9" s="139" t="str">
+        <x:v>Corporate Retreat</x:v>
+      </x:c>
+      <x:c r="B9" s="140" t="n">
+        <x:v>46150</x:v>
+      </x:c>
+      <x:c r="C9" s="140" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D9" s="140" t="n">
+        <x:v>3200</x:v>
+      </x:c>
+      <x:c r="E9" s="140" t="n">
+        <x:v>1990</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>Staffing</x:v>
-      </x:c>
-      <x:c r="B10" s="48"/>
-      <x:c r="C10" t="str">
-        <x:v>Type the slide given first</x:v>
+      <x:c r="A10" s="139" t="str">
+        <x:v>Summer Wedding</x:v>
+      </x:c>
+      <x:c r="B10" s="140" t="n">
+        <x:v>46194</x:v>
+      </x:c>
+      <x:c r="C10" s="140" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D10" s="140" t="n">
+        <x:v>9500</x:v>
+      </x:c>
+      <x:c r="E10" s="140" t="n">
+        <x:v>5510</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" t="str">
-        <x:v>Net Profit</x:v>
-      </x:c>
-      <x:c r="B11" s="49"/>
-      <x:c r="C11" t="str">
-        <x:v>Revenue − Catering − Staffing</x:v>
-      </x:c>
-      <x:c r="D11" s="47" t="str">
-        <x:f>IF(B11="","Enter a formula.",IF(ABS(B11-2980)&lt;=0.01,"Correct · Spring Gala net profit","Review the givens and cell references."))</x:f>
-        <x:v>Enter a formula.</x:v>
-      </x:c>
-      <x:c r="E11" s="47"/>
+      <x:c r="A11" s="139" t="str">
+        <x:v>Fall Gala</x:v>
+      </x:c>
+      <x:c r="B11" s="140" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="C11" s="140" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D11" s="140" t="n">
+        <x:v>5200</x:v>
+      </x:c>
+      <x:c r="E11" s="140" t="n">
+        <x:v>3290</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="139" t="str">
+        <x:v>Winter Fundraiser</x:v>
+      </x:c>
+      <x:c r="B12" s="140" t="n">
+        <x:v>46368</x:v>
+      </x:c>
+      <x:c r="C12" s="140" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D12" s="140" t="n">
+        <x:v>7400</x:v>
+      </x:c>
+      <x:c r="E12" s="140" t="n">
+        <x:v>4105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="139" t="str">
+        <x:v>Community Awards Brunch</x:v>
+      </x:c>
+      <x:c r="B13" s="140" t="n">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C13" s="140" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D13" s="140" t="n">
+        <x:v>4100</x:v>
+      </x:c>
+      <x:c r="E13" s="140" t="n">
+        <x:v>2215</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="17" t="str">
-        <x:v>Pause 2 · Four-event revenue total</x:v>
-      </x:c>
-      <x:c r="B15" s="17"/>
-      <x:c r="C15" s="17"/>
-      <x:c r="D15" s="17"/>
-      <x:c r="E15" s="17"/>
+      <x:c r="A15" s="142" t="str">
+        <x:v>Checkpoint 2 · 5 minutes · Make the table usable</x:v>
+      </x:c>
+      <x:c r="B15" s="142"/>
+      <x:c r="C15" s="142"/>
+      <x:c r="D15" s="142"/>
+      <x:c r="E15" s="142"/>
+    </x:row>
+    <x:row r="16" ht="58" customHeight="1">
+      <x:c r="A16" s="146" t="str">
+        <x:v>WHAT + HOW · Convert A7:E13 to an Excel table, keep its filters, select A8 and freeze the rows above it, then apply one conditional-formatting rule to E8:E13 for a business reason you can explain.</x:v>
+      </x:c>
+      <x:c r="B16" s="147"/>
+      <x:c r="C16" s="147"/>
+      <x:c r="D16" s="147"/>
+      <x:c r="E16" s="148"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="41" t="str">
-        <x:v>Step</x:v>
-      </x:c>
-      <x:c r="B17" s="41" t="str">
-        <x:v>Your Cell</x:v>
-      </x:c>
-      <x:c r="C17" s="41" t="str">
-        <x:v>Hint / Check</x:v>
-      </x:c>
-      <x:c r="D17" s="41" t="str">
-        <x:v>Feedback</x:v>
-      </x:c>
-      <x:c r="E17" s="41" t="str">
-        <x:v>Practice Status</x:v>
-      </x:c>
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" t="str">
-        <x:v>Spring Gala Revenue</x:v>
-      </x:c>
-      <x:c r="B18" s="48"/>
-      <x:c r="C18" t="str">
-        <x:v>Type the slide given first</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="str">
-        <x:v>Corporate Retreat Revenue</x:v>
-      </x:c>
-      <x:c r="B19" s="48"/>
-      <x:c r="C19" t="str">
-        <x:v>Type the slide given first</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" t="str">
-        <x:v>Summer Wedding Revenue</x:v>
-      </x:c>
-      <x:c r="B20" s="48"/>
-      <x:c r="C20" t="str">
-        <x:v>Type the slide given first</x:v>
-      </x:c>
+      <x:c r="A18" s="150" t="str">
+        <x:v>DELIVERABLE · A working table plus one purpose statement</x:v>
+      </x:c>
+      <x:c r="B18" s="150"/>
+      <x:c r="C18" s="150"/>
+      <x:c r="D18" s="150"/>
+      <x:c r="E18" s="150"/>
+    </x:row>
+    <x:row r="19" ht="34" customHeight="1">
+      <x:c r="A19" s="165" t="str">
+        <x:v>Type here: Highlight __________ because the manager needs to __________.</x:v>
+      </x:c>
+      <x:c r="B19" s="166"/>
+      <x:c r="C19" s="166"/>
+      <x:c r="D19" s="166"/>
+      <x:c r="E19" s="167"/>
+    </x:row>
+    <x:row r="20" ht="34" customHeight="1">
+      <x:c r="A20" s="168"/>
+      <x:c r="B20" s="169"/>
+      <x:c r="C20" s="169"/>
+      <x:c r="D20" s="169"/>
+      <x:c r="E20" s="170"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" t="str">
-        <x:v>Fall Gala Revenue</x:v>
-      </x:c>
-      <x:c r="B21" s="48"/>
-      <x:c r="C21" t="str">
-        <x:v>Type the slide given first</x:v>
-      </x:c>
+      <x:c r="A21"/>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" t="str">
-        <x:v>Total Revenue</x:v>
-      </x:c>
-      <x:c r="B22" s="49"/>
-      <x:c r="C22" t="str">
-        <x:v>SUM all four revenue cells</x:v>
-      </x:c>
-      <x:c r="D22" s="47" t="str">
-        <x:f>IF(B22="","Enter a formula.",IF(ABS(B22-22700)&lt;=0.01,"Correct · four-event revenue","Review the givens and cell references."))</x:f>
-        <x:v>Enter a formula.</x:v>
-      </x:c>
-      <x:c r="E22" s="47"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="17" t="str">
-        <x:v>Pause 3 · Four-event net profit total</x:v>
-      </x:c>
-      <x:c r="B26" s="17"/>
-      <x:c r="C26" s="17"/>
-      <x:c r="D26" s="17"/>
-      <x:c r="E26" s="17"/>
+      <x:c r="A22" s="104" t="str">
+        <x:v>Quick self-check before Manager View</x:v>
+      </x:c>
+      <x:c r="B22" s="104"/>
+      <x:c r="C22" s="104"/>
+      <x:c r="D22" s="104"/>
+      <x:c r="E22" s="104"/>
+    </x:row>
+    <x:row r="23" ht="30" customHeight="1">
+      <x:c r="A23" s="172" t="str">
+        <x:v>□</x:v>
+      </x:c>
+      <x:c r="B23" s="175" t="str">
+        <x:v>The same stored values remain in every practice cell.</x:v>
+      </x:c>
+      <x:c r="C23" s="175"/>
+      <x:c r="D23" s="175"/>
+      <x:c r="E23" s="175"/>
+    </x:row>
+    <x:row r="24" ht="30" customHeight="1">
+      <x:c r="A24" s="172" t="str">
+        <x:v>□</x:v>
+      </x:c>
+      <x:c r="B24" s="175" t="str">
+        <x:v>Dates, whole-number counts, and money are immediately recognizable.</x:v>
+      </x:c>
+      <x:c r="C24" s="175"/>
+      <x:c r="D24" s="175"/>
+      <x:c r="E24" s="175"/>
+    </x:row>
+    <x:row r="25" ht="30" customHeight="1">
+      <x:c r="A25" s="172" t="str">
+        <x:v>□</x:v>
+      </x:c>
+      <x:c r="B25" s="175" t="str">
+        <x:v>The header remains visible when you scroll below the table.</x:v>
+      </x:c>
+      <x:c r="C25" s="175"/>
+      <x:c r="D25" s="175"/>
+      <x:c r="E25" s="175"/>
+    </x:row>
+    <x:row r="26" ht="30" customHeight="1">
+      <x:c r="A26" s="172" t="str">
+        <x:v>□</x:v>
+      </x:c>
+      <x:c r="B26" s="175" t="str">
+        <x:v>You can explain what your conditional-formatting rule helps a manager notice.</x:v>
+      </x:c>
+      <x:c r="C26" s="175"/>
+      <x:c r="D26" s="175"/>
+      <x:c r="E26" s="175"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="41" t="str">
-        <x:v>Step</x:v>
-      </x:c>
-      <x:c r="B28" s="41" t="str">
-        <x:v>Your Cell</x:v>
-      </x:c>
-      <x:c r="C28" s="41" t="str">
-        <x:v>Hint / Check</x:v>
-      </x:c>
-      <x:c r="D28" s="41" t="str">
-        <x:v>Feedback</x:v>
-      </x:c>
-      <x:c r="E28" s="41" t="str">
-        <x:v>Practice Status</x:v>
-      </x:c>
+      <x:c r="A28"/>
+      <x:c r="B28"/>
+      <x:c r="C28"/>
+      <x:c r="D28"/>
+      <x:c r="E28"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" t="str">
-        <x:v>Spring Gala Net Profit</x:v>
-      </x:c>
-      <x:c r="B29" s="48"/>
-      <x:c r="C29" t="str">
-        <x:v>Type the slide given first</x:v>
-      </x:c>
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" t="str">
-        <x:v>Corporate Retreat Net Profit</x:v>
-      </x:c>
-      <x:c r="B30" s="48"/>
-      <x:c r="C30" t="str">
-        <x:v>Type the slide given first</x:v>
-      </x:c>
+      <x:c r="A30"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" t="str">
-        <x:v>Summer Wedding Net Profit</x:v>
-      </x:c>
-      <x:c r="B31" s="48"/>
-      <x:c r="C31" t="str">
-        <x:v>Type the slide given first</x:v>
-      </x:c>
+      <x:c r="A31"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" t="str">
-        <x:v>Fall Gala Net Profit</x:v>
-      </x:c>
-      <x:c r="B32" s="48"/>
-      <x:c r="C32" t="str">
-        <x:v>Type the slide given first</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" t="str">
-        <x:v>Total Net Profit</x:v>
-      </x:c>
-      <x:c r="B33" s="49"/>
-      <x:c r="C33" t="str">
-        <x:v>SUM all four net profit cells</x:v>
-      </x:c>
-      <x:c r="D33" s="47" t="str">
-        <x:f>IF(B33="","Enter a formula.",IF(ABS(B33-13770)&lt;=0.01,"Correct · four-event net profit","Review the givens and cell references."))</x:f>
-        <x:v>Enter a formula.</x:v>
-      </x:c>
-      <x:c r="E33" s="47"/>
+      <x:c r="A33"/>
+      <x:c r="B33"/>
+      <x:c r="C33"/>
+      <x:c r="D33"/>
+      <x:c r="E33"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A4:E4"/>
     <x:mergeCell ref="A5:E5"/>
+    <x:mergeCell ref="A6:E6"/>
     <x:mergeCell ref="A15:E15"/>
-    <x:mergeCell ref="A26:E26"/>
+    <x:mergeCell ref="A16:E16"/>
+    <x:mergeCell ref="A18:E18"/>
+    <x:mergeCell ref="A19:E20"/>
+    <x:mergeCell ref="A22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1964,21 +2477,21 @@
       <x:c r="K1" s="4"/>
       <x:c r="L1" s="4"/>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="7" t="str">
-        <x:v>Format this working copy. Preserve Raw Export exactly. Build summaries in the labeled cells, then complete the Class Challenge audit.</x:v>
-      </x:c>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
-      <x:c r="G2" s="7"/>
-      <x:c r="H2" s="7"/>
-      <x:c r="I2" s="7"/>
-      <x:c r="J2" s="7"/>
-      <x:c r="K2" s="7"/>
-      <x:c r="L2" s="7"/>
+    <x:row r="2" ht="32" customHeight="1">
+      <x:c r="A2" s="97" t="str">
+        <x:v>Begin only when your instructor directs you. Preserve Raw Export exactly; build the working table and summaries here, then complete the Class Challenge audit.</x:v>
+      </x:c>
+      <x:c r="B2" s="97"/>
+      <x:c r="C2" s="97"/>
+      <x:c r="D2" s="97"/>
+      <x:c r="E2" s="97"/>
+      <x:c r="F2" s="97"/>
+      <x:c r="G2" s="97"/>
+      <x:c r="H2" s="97"/>
+      <x:c r="I2" s="97"/>
+      <x:c r="J2" s="97"/>
+      <x:c r="K2" s="97"/>
+      <x:c r="L2" s="97"/>
     </x:row>
     <x:row r="3">
       <x:c r="B3" s="53" t="str">
@@ -2001,21 +2514,21 @@
       </x:c>
       <x:c r="L3" s="54"/>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="56" t="str">
-        <x:v>Student workspace · Convert A7:J31 to an Excel table with filters. Do not merge cells inside the data table.</x:v>
-      </x:c>
-      <x:c r="B5" s="56"/>
-      <x:c r="C5" s="56"/>
-      <x:c r="D5" s="56"/>
-      <x:c r="E5" s="56"/>
-      <x:c r="F5" s="56"/>
-      <x:c r="G5" s="56"/>
-      <x:c r="H5" s="56"/>
-      <x:c r="I5" s="56"/>
-      <x:c r="J5" s="56"/>
-      <x:c r="K5" s="56"/>
-      <x:c r="L5" s="56"/>
+    <x:row r="5" ht="34" customHeight="1">
+      <x:c r="A5" s="177" t="str">
+        <x:v>IN CLASS · Convert A7:J31 to one Excel table with filters; format dates, counts, and money; set readable widths and alignment; then select A8 and freeze the rows above it.</x:v>
+      </x:c>
+      <x:c r="B5" s="177"/>
+      <x:c r="C5" s="177"/>
+      <x:c r="D5" s="177"/>
+      <x:c r="E5" s="177"/>
+      <x:c r="F5" s="177"/>
+      <x:c r="G5" s="177"/>
+      <x:c r="H5" s="177"/>
+      <x:c r="I5" s="177"/>
+      <x:c r="J5" s="177"/>
+      <x:c r="K5" s="177"/>
+      <x:c r="L5" s="177"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="72" t="str">
@@ -2831,233 +3344,233 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="42" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="38" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="44" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="39" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
-        <x:v>Class Challenge · Raw Export Makeover</x:v>
-      </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="7" t="str">
-        <x:v>Begin in class and finish for homework. Your deliverable is the completed Manager View; Raw Export must remain unchanged.</x:v>
-      </x:c>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
+      <x:c r="A1" s="96" t="str">
+        <x:v>Class Challenge · Manager View Handoff</x:v>
+      </x:c>
+      <x:c r="B1" s="96"/>
+      <x:c r="C1" s="96"/>
+      <x:c r="D1" s="96"/>
+      <x:c r="E1" s="96"/>
+    </x:row>
+    <x:row r="2" ht="38" customHeight="1">
+      <x:c r="A2" s="97" t="str">
+        <x:v>Begin only when your instructor directs you. The completed Manager View is graded; Live You Try It remains ungraded practice and Raw Export must remain unchanged.</x:v>
+      </x:c>
+      <x:c r="B2" s="97"/>
+      <x:c r="C2" s="97"/>
+      <x:c r="D2" s="97"/>
+      <x:c r="E2" s="97"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="41" t="str">
+      <x:c r="A4" s="111" t="str">
         <x:v>Step</x:v>
       </x:c>
-      <x:c r="B4" s="41" t="str">
+      <x:c r="B4" s="111" t="str">
         <x:v>Requirement</x:v>
       </x:c>
-      <x:c r="C4" s="41" t="str">
+      <x:c r="C4" s="111" t="str">
         <x:v>Where</x:v>
       </x:c>
-      <x:c r="D4" s="41" t="str">
-        <x:v>Automatically checked</x:v>
-      </x:c>
-      <x:c r="E4" s="41" t="str">
+      <x:c r="D4" s="111" t="str">
+        <x:v>When</x:v>
+      </x:c>
+      <x:c r="E4" s="111" t="str">
         <x:v>Completion evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="58" customHeight="1">
-      <x:c r="A5" s="76" t="str">
+    <x:row r="5" ht="52" customHeight="1">
+      <x:c r="A5" s="181" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="15" t="str">
+      <x:c r="B5" s="101" t="str">
         <x:v>Preserve every Raw Export header and record exactly as provided.</x:v>
       </x:c>
-      <x:c r="C5" s="15" t="str">
+      <x:c r="C5" s="101" t="str">
         <x:v>Raw Export!A1:J25</x:v>
       </x:c>
-      <x:c r="D5" s="15" t="str">
-        <x:v>Yes · data integrity</x:v>
-      </x:c>
-      <x:c r="E5" s="15" t="str">
+      <x:c r="D5" s="101" t="str">
+        <x:v>Always</x:v>
+      </x:c>
+      <x:c r="E5" s="101" t="str">
         <x:v>No values, rows, columns, or sheet names changed</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="58" customHeight="1">
-      <x:c r="A6" s="76" t="str">
+    <x:row r="6" ht="52" customHeight="1">
+      <x:c r="A6" s="181" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B6" s="15" t="str">
+      <x:c r="B6" s="101" t="str">
         <x:v>Convert the full manager data range into one Excel table and keep filter buttons available.</x:v>
       </x:c>
-      <x:c r="C6" s="15" t="str">
+      <x:c r="C6" s="101" t="str">
         <x:v>Manager View!A7:J31</x:v>
       </x:c>
-      <x:c r="D6" s="15" t="str">
-        <x:v>Yes · table range + filters</x:v>
-      </x:c>
-      <x:c r="E6" s="15" t="str">
+      <x:c r="D6" s="101" t="str">
+        <x:v>In class</x:v>
+      </x:c>
+      <x:c r="E6" s="101" t="str">
         <x:v>All 24 records and headers are inside one table</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="58" customHeight="1">
-      <x:c r="A7" s="76" t="str">
+    <x:row r="7" ht="52" customHeight="1">
+      <x:c r="A7" s="181" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B7" s="15" t="str">
-        <x:v>Use meaningful formats: date, whole-number guests, and business currency for Revenue through Net Profit.</x:v>
-      </x:c>
-      <x:c r="C7" s="15" t="str">
+      <x:c r="B7" s="101" t="str">
+        <x:v>Use meaningful formats for the date, whole-number Guests, and business-money columns.</x:v>
+      </x:c>
+      <x:c r="C7" s="101" t="str">
         <x:v>Manager View</x:v>
       </x:c>
-      <x:c r="D7" s="15" t="str">
-        <x:v>Yes · number formats</x:v>
-      </x:c>
-      <x:c r="E7" s="15" t="str">
-        <x:v>Formats communicate what each column means</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="58" customHeight="1">
-      <x:c r="A8" s="76" t="str">
+      <x:c r="D7" s="101" t="str">
+        <x:v>In class</x:v>
+      </x:c>
+      <x:c r="E7" s="101" t="str">
+        <x:v>Every format communicates what its column means</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="52" customHeight="1">
+      <x:c r="A8" s="181" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B8" s="15" t="str">
-        <x:v>Set readable column widths and align text/numbers so the manager can scan without avoidable clipping.</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="str">
+      <x:c r="B8" s="101" t="str">
+        <x:v>Set readable widths and alignment so long labels and values can be scanned without avoidable clipping.</x:v>
+      </x:c>
+      <x:c r="C8" s="101" t="str">
         <x:v>Manager View!A:J</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="str">
-        <x:v>Yes · minimum widths</x:v>
-      </x:c>
-      <x:c r="E8" s="15" t="str">
-        <x:v>Long event names and headings are readable</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="58" customHeight="1">
-      <x:c r="A9" s="76" t="str">
+      <x:c r="D8" s="101" t="str">
+        <x:v>In class</x:v>
+      </x:c>
+      <x:c r="E8" s="101" t="str">
+        <x:v>Event names and headings are readable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="52" customHeight="1">
+      <x:c r="A9" s="181" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B9" s="15" t="str">
-        <x:v>Freeze the table header row so labels stay visible while scrolling.</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="str">
+      <x:c r="B9" s="101" t="str">
+        <x:v>Select A8 and freeze the rows above it so the actual table header remains visible.</x:v>
+      </x:c>
+      <x:c r="C9" s="101" t="str">
         <x:v>Manager View</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="str">
-        <x:v>Yes · Freeze Panes</x:v>
-      </x:c>
-      <x:c r="E9" s="15" t="str">
-        <x:v>Row 7 remains visible below the frozen pane</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="58" customHeight="1">
-      <x:c r="A10" s="76" t="str">
+      <x:c r="D9" s="101" t="str">
+        <x:v>In class</x:v>
+      </x:c>
+      <x:c r="E9" s="101" t="str">
+        <x:v>Row 7 remains visible while scrolling</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="52" customHeight="1">
+      <x:c r="A10" s="181" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B10" s="15" t="str">
-        <x:v>Build four formulas in the labeled summary cells for Total Revenue, Total Net Profit, Average Revenue per Event, and Total Guests.</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="str">
+      <x:c r="B10" s="101" t="str">
+        <x:v>Build the four labeled summaries for Total Revenue, Total Net Profit, Average Revenue per Event, and Total Guests.</x:v>
+      </x:c>
+      <x:c r="C10" s="101" t="str">
         <x:v>Manager View!C3, F3, I3, L3</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="str">
-        <x:v>Yes · formula + result</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="str">
-        <x:v>Use cell/table references; do not type totals</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="58" customHeight="1">
-      <x:c r="A11" s="76" t="str">
+      <x:c r="D10" s="101" t="str">
+        <x:v>After class</x:v>
+      </x:c>
+      <x:c r="E10" s="101" t="str">
+        <x:v>Each result is a formula using worksheet or table references</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="52" customHeight="1">
+      <x:c r="A11" s="181" t="str">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B11" s="15" t="str">
-        <x:v>Apply at least one purposeful conditional-formatting rule to Net Profit.</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="str">
+      <x:c r="B11" s="101" t="str">
+        <x:v>Apply one conditional-formatting rule to Net Profit and be able to state its business purpose.</x:v>
+      </x:c>
+      <x:c r="C11" s="101" t="str">
         <x:v>Manager View!I8:I31</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="str">
-        <x:v>Yes · conditional formatting</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="str">
-        <x:v>The rule helps identify high, low, or risky results</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="58" customHeight="1">
-      <x:c r="A12" s="76" t="str">
+      <x:c r="D11" s="101" t="str">
+        <x:v>After class</x:v>
+      </x:c>
+      <x:c r="E11" s="101" t="str">
+        <x:v>The rule helps identify a high, low, or risky result</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="52" customHeight="1">
+      <x:c r="A12" s="181" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B12" s="15" t="str">
-        <x:v>Create a clear visual hierarchy with a readable table, distinct summaries, and purposeful emphasis. Any professional palette is acceptable.</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="str">
+      <x:c r="B12" s="101" t="str">
+        <x:v>Create a clear visual hierarchy with readable summaries, a usable table, and purposeful emphasis.</x:v>
+      </x:c>
+      <x:c r="C12" s="101" t="str">
         <x:v>Manager View</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="str">
-        <x:v>3-point flagged spot-check</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="str">
-        <x:v>The workbook is understandable in about 30 seconds</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="58" customHeight="1">
-      <x:c r="A13" s="76" t="str">
+      <x:c r="D12" s="101" t="str">
+        <x:v>Final audit</x:v>
+      </x:c>
+      <x:c r="E12" s="101" t="str">
+        <x:v>A manager can understand the workbook in about 30 seconds</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="52" customHeight="1">
+      <x:c r="A13" s="181" t="str">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B13" s="15" t="str">
-        <x:v>Save and submit the original .xlsx with required sheet names intact.</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="str">
+      <x:c r="B13" s="101" t="str">
+        <x:v>Save and submit the original .xlsx with all required sheet names intact.</x:v>
+      </x:c>
+      <x:c r="C13" s="101" t="str">
         <x:v>Whole workbook</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="str">
-        <x:v>Yes · structure</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="str">
-        <x:v>Workbook opens normally in Excel</x:v>
+      <x:c r="D13" s="101" t="str">
+        <x:v>Submit</x:v>
+      </x:c>
+      <x:c r="E13" s="101" t="str">
+        <x:v>Workbook opens normally; do not submit PDF or CSV</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="81" t="str">
+      <x:c r="A15" s="182" t="str">
         <x:v>Timing</x:v>
       </x:c>
-      <x:c r="B15" s="81" t="str">
+      <x:c r="B15" s="182" t="str">
         <x:v>In class · about 25 minutes</x:v>
       </x:c>
-      <x:c r="C15" s="81" t="str">
-        <x:v>Homework · about 30–40 minutes</x:v>
-      </x:c>
-      <x:c r="D15" s="81" t="str">
-        <x:v>Auto/manual split</x:v>
-      </x:c>
-      <x:c r="E15" s="81" t="str">
+      <x:c r="C15" s="182" t="str">
+        <x:v>After class · about 30–40 minutes</x:v>
+      </x:c>
+      <x:c r="D15" s="182" t="str">
+        <x:v>Grading</x:v>
+      </x:c>
+      <x:c r="E15" s="182" t="str">
         <x:v>Submission</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="60" customHeight="1">
-      <x:c r="A16" s="15" t="str">
+    <x:row r="16" ht="54" customHeight="1">
+      <x:c r="A16" s="101" t="str">
         <x:v>Start the structure before you leave class.</x:v>
       </x:c>
-      <x:c r="B16" s="15" t="str">
+      <x:c r="B16" s="101" t="str">
         <x:v>Table, filters, widths, alignment, number formats, Freeze Panes</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="str">
-        <x:v>Four formulas, conditional formatting, 30-second audit</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="str">
+      <x:c r="C16" s="101" t="str">
+        <x:v>Four formulas, one purposeful rule, 30-second audit</x:v>
+      </x:c>
+      <x:c r="D16" s="101" t="str">
         <x:v>27 automatic + 3 visual spot-check = 30 points</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="str">
-        <x:v>Upload the completed .xlsx; do not submit PDF/CSV</x:v>
+      <x:c r="E16" s="101" t="str">
+        <x:v>Upload the completed .xlsx; do not submit PDF or CSV</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3073,108 +3586,136 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="23" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="36" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="31" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="40" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="41" t="str">
+      <x:c r="A1" s="186" t="str">
         <x:v>Concept</x:v>
       </x:c>
-      <x:c r="B1" s="41" t="str">
-        <x:v>Excel pattern</x:v>
-      </x:c>
-      <x:c r="C1" s="41" t="str">
+      <x:c r="B1" s="186" t="str">
+        <x:v>Excel pattern / action</x:v>
+      </x:c>
+      <x:c r="C1" s="186" t="str">
         <x:v>Plain-English meaning</x:v>
       </x:c>
-      <x:c r="D1" s="41" t="str">
+      <x:c r="D1" s="186" t="str">
         <x:v>Watch out for</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="24" t="str">
-        <x:v>Total</x:v>
-      </x:c>
-      <x:c r="B2" s="89" t="str">
-        <x:v>=SUM(F8:F31)</x:v>
-      </x:c>
-      <x:c r="C2" s="84" t="str">
-        <x:v>Adds the full Revenue column.</x:v>
-      </x:c>
-      <x:c r="D2" s="92" t="str">
-        <x:v>Do not type the total as a value.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="26" t="str">
-        <x:v>Average</x:v>
-      </x:c>
-      <x:c r="B3" s="90" t="str">
-        <x:v>=AVERAGE(F8:F31)</x:v>
-      </x:c>
-      <x:c r="C3" s="14" t="str">
-        <x:v>Finds average revenue per event.</x:v>
-      </x:c>
-      <x:c r="D3" s="93" t="str">
-        <x:v>Include detail rows only.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="26" t="str">
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="101" t="str">
+        <x:v>Total a numeric column</x:v>
+      </x:c>
+      <x:c r="B2" s="189" t="str">
+        <x:v>=SUM(number_range)</x:v>
+      </x:c>
+      <x:c r="C2" s="101" t="str">
+        <x:v>Adds all detail values in the selected range.</x:v>
+      </x:c>
+      <x:c r="D2" s="190" t="str">
+        <x:v>Do not type the final total as a value.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="42" customHeight="1">
+      <x:c r="A3" s="101" t="str">
+        <x:v>Average a numeric column</x:v>
+      </x:c>
+      <x:c r="B3" s="189" t="str">
+        <x:v>=AVERAGE(number_range)</x:v>
+      </x:c>
+      <x:c r="C3" s="101" t="str">
+        <x:v>Finds the arithmetic mean of the selected detail values.</x:v>
+      </x:c>
+      <x:c r="D3" s="190" t="str">
+        <x:v>Do not include labels or summary cells.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="42" customHeight="1">
+      <x:c r="A4" s="101" t="str">
         <x:v>Date format</x:v>
       </x:c>
-      <x:c r="B4" s="90" t="str">
+      <x:c r="B4" s="189" t="str">
         <x:v>dd-mmm-yy</x:v>
       </x:c>
-      <x:c r="C4" s="14" t="str">
-        <x:v>Shows a real date consistently.</x:v>
-      </x:c>
-      <x:c r="D4" s="93" t="str">
+      <x:c r="C4" s="101" t="str">
+        <x:v>Displays a real Excel date consistently.</x:v>
+      </x:c>
+      <x:c r="D4" s="190" t="str">
         <x:v>Formatting cannot convert text into a date.</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="26" t="str">
-        <x:v>Currency format</x:v>
-      </x:c>
-      <x:c r="B5" s="90" t="str">
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="101" t="str">
+        <x:v>Business money</x:v>
+      </x:c>
+      <x:c r="B5" s="189" t="str">
         <x:v>$#,##0</x:v>
       </x:c>
-      <x:c r="C5" s="14" t="str">
-        <x:v>Signals that values are dollars.</x:v>
-      </x:c>
-      <x:c r="D5" s="93" t="str">
-        <x:v>Choose a consistent decimal policy.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="C5" s="101" t="str">
+        <x:v>Signals dollars with a consistent decimal policy.</x:v>
+      </x:c>
+      <x:c r="D5" s="190" t="str">
+        <x:v>Use one policy throughout related columns.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="101" t="str">
         <x:v>Excel table</x:v>
       </x:c>
-      <x:c r="B6" s="90" t="str">
-        <x:v>A7:J31</x:v>
-      </x:c>
-      <x:c r="C6" s="14" t="str">
+      <x:c r="B6" s="189" t="str">
+        <x:v>Select the full range</x:v>
+      </x:c>
+      <x:c r="C6" s="101" t="str">
         <x:v>Adds structure, banding, and filters.</x:v>
       </x:c>
-      <x:c r="D6" s="93" t="str">
+      <x:c r="D6" s="190" t="str">
         <x:v>Include every header and all 24 records.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="28" t="str">
-        <x:v>Freeze Panes</x:v>
-      </x:c>
-      <x:c r="B7" s="91" t="str">
-        <x:v>Freeze above row 8</x:v>
-      </x:c>
-      <x:c r="C7" s="85" t="str">
-        <x:v>Keeps row 7 headers visible.</x:v>
-      </x:c>
-      <x:c r="D7" s="94" t="str">
-        <x:v>Freeze after the actual table header.</x:v>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="101" t="str">
+        <x:v>Freeze the M02 header</x:v>
+      </x:c>
+      <x:c r="B7" s="189" t="str">
+        <x:v>Select A8, then Freeze Panes</x:v>
+      </x:c>
+      <x:c r="C7" s="101" t="str">
+        <x:v>Keeps rows 1–7 visible while records scroll.</x:v>
+      </x:c>
+      <x:c r="D7" s="190" t="str">
+        <x:v>Freeze below the actual row 7 table header.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="101" t="str">
+        <x:v>Purposeful alert</x:v>
+      </x:c>
+      <x:c r="B8" s="189" t="str">
+        <x:v>Conditional Formatting</x:v>
+      </x:c>
+      <x:c r="C8" s="101" t="str">
+        <x:v>Calls attention to a result that needs review.</x:v>
+      </x:c>
+      <x:c r="D8" s="190" t="str">
+        <x:v>Be able to name the business reason and range.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="101" t="str">
+        <x:v>Auditable formula</x:v>
+      </x:c>
+      <x:c r="B9" s="189" t="str">
+        <x:v>Reference worksheet cells</x:v>
+      </x:c>
+      <x:c r="C9" s="101" t="str">
+        <x:v>Updates when a source value changes.</x:v>
+      </x:c>
+      <x:c r="D9" s="190" t="str">
+        <x:v>Do not hardcode totals inside formulas.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/EXCEL/M02/bus123-excel-m02-l01-starter.xlsx
+++ b/EXCEL/M02/bus123-excel-m02-l01-starter.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R8b6792c39a07466a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R426c2f86b4ec451f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Export" sheetId="3" r:id="Rcdd3080958da45df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manager View" sheetId="4" r:id="R5b721644b4ff405f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="5" r:id="R667e9741eef24096"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="6" r:id="R605b5a3efd014808"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Reb27bf64c1e84923"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="Rb9af3a372f924282"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Export" sheetId="3" r:id="R944fc666fb644469"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manager View" sheetId="4" r:id="Rb50bf440824249b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="5" r:id="R27ef597b93b84559"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="6" r:id="R91f20e56d7714e06"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,7 +22,7 @@
     <x:numFmt numFmtId="200" formatCode="$#,##0"/>
     <x:numFmt numFmtId="201" formatCode="General"/>
   </x:numFmts>
-  <x:fonts count="20">
+  <x:fonts count="23">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -138,8 +138,25 @@
       <x:color rgb="FF355773"/>
       <x:name val="Aptos Mono"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF111827"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF111827"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF355773"/>
+      <x:name val="Aptos"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="19">
+  <x:fills count="22">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -231,8 +248,23 @@
         <x:fgColor rgb="FFF7E7E0"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0E1116"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4A7C5E"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="35">
+  <x:borders count="44">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -542,11 +574,113 @@
         <x:color rgb="FFD9B44A"/>
       </x:bottom>
     </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none"/>
+      <x:right style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:right>
+      <x:top style="none"/>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:bottom>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:right>
+      <x:top style="none"/>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:bottom>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:left>
+      <x:right style="none"/>
+      <x:top style="none"/>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:bottom>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none"/>
+      <x:right style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:bottom>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:bottom>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:left>
+      <x:right style="none"/>
+      <x:top style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:bottom>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none"/>
+      <x:right style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:top>
+      <x:bottom style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:top>
+      <x:bottom style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:left>
+      <x:right style="none"/>
+      <x:top style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:top>
+      <x:bottom style="none"/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="191">
+  <x:cellXfs count="271">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -937,6 +1071,204 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="19" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="19" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="19" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="19" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="20" fillId="19" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="20" fillId="19" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="20" fillId="19" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="20" fillId="19" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="20" fillId="19" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="20" fillId="19" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="20" fillId="19" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="20" fillId="19" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="20" fillId="19" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="19" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="19" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="19" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="19" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="21" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1181,10 +1513,10 @@
         <x:v>Read the pre-reading. Open this workbook only to observe the tabs. Do not edit Raw Export or begin Manager View yet.</x:v>
       </x:c>
       <x:c r="B5" s="101" t="str">
-        <x:v>Complete the two Live You Try It formatting checkpoints when the slides direct you. The supplied data is already entered; focus on formatting decisions.</x:v>
+        <x:v>Complete the two Live You Try It checkpoints when the slides direct you. The supplied Tidal Goods data is different from the graded Anchor &amp; Oak challenge; focus on formatting decisions.</x:v>
       </x:c>
       <x:c r="C5" s="101" t="str">
-        <x:v>When directed, preserve Raw Export and spend about 25 minutes building the Manager View structure: table, filters, formats, widths, alignment, and Freeze Panes.</x:v>
+        <x:v>When directed, preserve Raw Export, copy its 10 headers and 24 records, paste values at Manager View!A7, rename the headers, and build the table, formats, widths, alignment, and Freeze Panes.</x:v>
       </x:c>
       <x:c r="D5" s="101" t="str">
         <x:v>Finish four summary formulas, one purposeful conditional-formatting rule, and the 30-second audit. Upload the completed original .xlsx.</x:v>
@@ -1203,8 +1535,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="108" t="str">
-        <x:v>Preserve source data while creating a separate working view.</x:v>
-      </x:c>
+        <x:v>Copy source data into a separate working view without changing the source.</x:v>
+      </x:c>
+      <x:c r="C9"/>
+      <x:c r="D9"/>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
       <x:c r="A10" s="106" t="str">
@@ -1213,6 +1547,8 @@
       <x:c r="B10" s="109" t="str">
         <x:v>Apply meaningful date, whole-number, and business currency formats.</x:v>
       </x:c>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
       <x:c r="A11" s="106" t="str">
@@ -1221,6 +1557,8 @@
       <x:c r="B11" s="109" t="str">
         <x:v>Use tables, filters, Freeze Panes, alignment, and readable widths to support scanning.</x:v>
       </x:c>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
       <x:c r="A12" s="106" t="str">
@@ -1229,6 +1567,8 @@
       <x:c r="B12" s="109" t="str">
         <x:v>Build auditable summary formulas with worksheet or table references.</x:v>
       </x:c>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
       <x:c r="A13" s="106" t="str">
@@ -1237,6 +1577,8 @@
       <x:c r="B13" s="109" t="str">
         <x:v>Apply conditional formatting for a named business purpose.</x:v>
       </x:c>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
       <x:c r="A14" s="107" t="str">
@@ -1245,6 +1587,8 @@
       <x:c r="B14" s="110" t="str">
         <x:v>Use visual hierarchy without relying on one prescribed palette or layout style.</x:v>
       </x:c>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="111" t="str">
@@ -1297,7 +1641,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="114" t="str">
-        <x:v>Live You Try It · Formatting Practice</x:v>
+        <x:v>Tidal Goods Co. · Live You Try It</x:v>
       </x:c>
       <x:c r="B1" s="114"/>
       <x:c r="C1" s="114"/>
@@ -1306,7 +1650,7 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="117" t="str">
-        <x:v>The event data is already entered. Make formatting decisions instead of retyping slide values. This sheet is not graded.</x:v>
+        <x:v>This guided retail dataset is different from the graded Anchor &amp; Oak challenge. Make formatting decisions without changing the supplied values. This sheet is not graded.</x:v>
       </x:c>
       <x:c r="B2" s="117"/>
       <x:c r="C2" s="117"/>
@@ -1315,7 +1659,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="104" t="str">
-        <x:v>Checkpoint 1 · 6 minutes · Make the supplied records readable</x:v>
+        <x:v>Checkpoint 1 · 6 minutes · Make the supplied retail records readable</x:v>
       </x:c>
       <x:c r="B4" s="104"/>
       <x:c r="C4" s="104"/>
@@ -1324,7 +1668,7 @@
     </x:row>
     <x:row r="5" ht="42" customHeight="1">
       <x:c r="A5" s="127" t="str">
-        <x:v>WHAT + HOW · Format Event Date as a readable date, Guests as a whole number, and Revenue / Net Profit as business money. Then make the headers and widths easy to scan.</x:v>
+        <x:v>WHAT + HOW · Format Sale Date as a readable date, Units Sold as a whole number, and Sales Revenue / Gross Profit as business money. Then make the headers and widths easy to scan.</x:v>
       </x:c>
       <x:c r="B5" s="128"/>
       <x:c r="C5" s="128"/>
@@ -1333,7 +1677,7 @@
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="130" t="str">
-        <x:v>DELIVERABLE · A six-row practice table whose dates, counts, money, labels, and alignment communicate clearly without changing any value.</x:v>
+        <x:v>DELIVERABLE · A six-row practice table whose dates, counts, money, labels, and alignment communicate clearly without changing any supplied value.</x:v>
       </x:c>
       <x:c r="B6" s="131"/>
       <x:c r="C6" s="131"/>
@@ -1342,121 +1686,121 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="136" t="str">
-        <x:v>Event</x:v>
+        <x:v>Product</x:v>
       </x:c>
       <x:c r="B7" s="136" t="str">
-        <x:v>Event Date</x:v>
+        <x:v>Sale Date</x:v>
       </x:c>
       <x:c r="C7" s="136" t="str">
-        <x:v>Guests</x:v>
+        <x:v>Units Sold</x:v>
       </x:c>
       <x:c r="D7" s="136" t="str">
-        <x:v>Revenue</x:v>
+        <x:v>Sales Revenue</x:v>
       </x:c>
       <x:c r="E7" s="136" t="str">
-        <x:v>Net Profit</x:v>
+        <x:v>Gross Profit</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="139" t="str">
-        <x:v>Spring Gala</x:v>
+        <x:v>Coastal Tote</x:v>
       </x:c>
       <x:c r="B8" s="140" t="n">
-        <x:v>46096</x:v>
+        <x:v>46087</x:v>
       </x:c>
       <x:c r="C8" s="140" t="n">
-        <x:v>120</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D8" s="140" t="n">
-        <x:v>4800</x:v>
+        <x:v>3040</x:v>
       </x:c>
       <x:c r="E8" s="140" t="n">
-        <x:v>2980</x:v>
+        <x:v>1216</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="139" t="str">
-        <x:v>Corporate Retreat</x:v>
+        <x:v>Insulated Bottle</x:v>
       </x:c>
       <x:c r="B9" s="140" t="n">
-        <x:v>46150</x:v>
+        <x:v>46095</x:v>
       </x:c>
       <x:c r="C9" s="140" t="n">
-        <x:v>55</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D9" s="140" t="n">
-        <x:v>3200</x:v>
+        <x:v>1680</x:v>
       </x:c>
       <x:c r="E9" s="140" t="n">
-        <x:v>1990</x:v>
+        <x:v>672</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="139" t="str">
-        <x:v>Summer Wedding</x:v>
+        <x:v>Canvas Apron</x:v>
       </x:c>
       <x:c r="B10" s="140" t="n">
-        <x:v>46194</x:v>
+        <x:v>46114</x:v>
       </x:c>
       <x:c r="C10" s="140" t="n">
-        <x:v>200</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D10" s="140" t="n">
-        <x:v>9500</x:v>
+        <x:v>1360</x:v>
       </x:c>
       <x:c r="E10" s="140" t="n">
-        <x:v>5510</x:v>
+        <x:v>544</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="139" t="str">
-        <x:v>Fall Gala</x:v>
+        <x:v>Bamboo Tray</x:v>
       </x:c>
       <x:c r="B11" s="140" t="n">
-        <x:v>46299</x:v>
+        <x:v>46131</x:v>
       </x:c>
       <x:c r="C11" s="140" t="n">
-        <x:v>95</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D11" s="140" t="n">
-        <x:v>5200</x:v>
+        <x:v>2480</x:v>
       </x:c>
       <x:c r="E11" s="140" t="n">
-        <x:v>3290</x:v>
+        <x:v>868</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="139" t="str">
-        <x:v>Winter Fundraiser</x:v>
+        <x:v>Ceramic Mug</x:v>
       </x:c>
       <x:c r="B12" s="140" t="n">
-        <x:v>46368</x:v>
+        <x:v>46149</x:v>
       </x:c>
       <x:c r="C12" s="140" t="n">
-        <x:v>150</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D12" s="140" t="n">
-        <x:v>7400</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="E12" s="140" t="n">
-        <x:v>4105</x:v>
+        <x:v>810</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="139" t="str">
-        <x:v>Community Awards Brunch</x:v>
+        <x:v>Storage Basket</x:v>
       </x:c>
       <x:c r="B13" s="140" t="n">
-        <x:v>46250</x:v>
+        <x:v>46165</x:v>
       </x:c>
       <x:c r="C13" s="140" t="n">
-        <x:v>85</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D13" s="140" t="n">
-        <x:v>4100</x:v>
+        <x:v>1520</x:v>
       </x:c>
       <x:c r="E13" s="140" t="n">
-        <x:v>2215</x:v>
+        <x:v>532</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1470,7 +1814,7 @@
     </x:row>
     <x:row r="16" ht="58" customHeight="1">
       <x:c r="A16" s="146" t="str">
-        <x:v>WHAT + HOW · Convert A7:E13 to an Excel table, keep its filters, select A8 and freeze the rows above it, then apply one conditional-formatting rule to E8:E13 for a business reason you can explain.</x:v>
+        <x:v>WHAT + HOW · Convert A7:E13 to an Excel table, keep its filters, select A8 and freeze the rows above it, then apply one conditional-formatting rule to E8:E13 for a retail decision you can explain.</x:v>
       </x:c>
       <x:c r="B16" s="147"/>
       <x:c r="C16" s="147"/>
@@ -1495,7 +1839,7 @@
     </x:row>
     <x:row r="19" ht="34" customHeight="1">
       <x:c r="A19" s="165" t="str">
-        <x:v>Type here: Highlight __________ because the manager needs to __________.</x:v>
+        <x:v>Type here: Highlight __________ because the retail manager needs to __________.</x:v>
       </x:c>
       <x:c r="B19" s="166"/>
       <x:c r="C19" s="166"/>
@@ -1516,7 +1860,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="104" t="str">
-        <x:v>Quick self-check before Manager View</x:v>
+        <x:v>Quick self-check before the Anchor &amp; Oak challenge</x:v>
       </x:c>
       <x:c r="B22" s="104"/>
       <x:c r="C22" s="104"/>
@@ -1528,7 +1872,7 @@
         <x:v>□</x:v>
       </x:c>
       <x:c r="B23" s="175" t="str">
-        <x:v>The same stored values remain in every practice cell.</x:v>
+        <x:v>The same stored values remain in every Tidal Goods practice cell.</x:v>
       </x:c>
       <x:c r="C23" s="175"/>
       <x:c r="D23" s="175"/>
@@ -1550,7 +1894,7 @@
         <x:v>□</x:v>
       </x:c>
       <x:c r="B25" s="175" t="str">
-        <x:v>The header remains visible when you scroll below the table.</x:v>
+        <x:v>The row 7 header remains visible when you scroll below the table.</x:v>
       </x:c>
       <x:c r="C25" s="175"/>
       <x:c r="D25" s="175"/>
@@ -1561,7 +1905,7 @@
         <x:v>□</x:v>
       </x:c>
       <x:c r="B26" s="175" t="str">
-        <x:v>You can explain what your conditional-formatting rule helps a manager notice.</x:v>
+        <x:v>You can explain what your conditional-formatting rule helps a retail manager notice.</x:v>
       </x:c>
       <x:c r="C26" s="175"/>
       <x:c r="D26" s="175"/>
@@ -2479,7 +2823,7 @@
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="97" t="str">
-        <x:v>Begin only when your instructor directs you. Preserve Raw Export exactly; build the working table and summaries here, then complete the Class Challenge audit.</x:v>
+        <x:v>Begin only when your instructor directs you. Copy Raw Export!A1:J25, paste values at A7, replace the snake_case headers with readable labels, then build the working table and summaries here.</x:v>
       </x:c>
       <x:c r="B2" s="97"/>
       <x:c r="C2" s="97"/>
@@ -2516,7 +2860,7 @@
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
       <x:c r="A5" s="177" t="str">
-        <x:v>IN CLASS · Convert A7:J31 to one Excel table with filters; format dates, counts, and money; set readable widths and alignment; then select A8 and freeze the rows above it.</x:v>
+        <x:v>IN CLASS · Copy Raw Export!A1:J25 → Paste Values at A7 → rename the 10 headers → convert A7:J31 to a table → format, align, size, and freeze at A8.</x:v>
       </x:c>
       <x:c r="B5" s="177"/>
       <x:c r="C5" s="177"/>
@@ -2531,804 +2875,304 @@
       <x:c r="L5" s="177"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="72" t="str">
-        <x:v>Event ID</x:v>
-      </x:c>
-      <x:c r="B7" s="73" t="str">
-        <x:v>Event</x:v>
-      </x:c>
-      <x:c r="C7" s="73" t="str">
-        <x:v>Event Date</x:v>
-      </x:c>
-      <x:c r="D7" s="73" t="str">
-        <x:v>Event Type</x:v>
-      </x:c>
-      <x:c r="E7" s="73" t="str">
-        <x:v>Guests</x:v>
-      </x:c>
-      <x:c r="F7" s="73" t="str">
-        <x:v>Revenue</x:v>
-      </x:c>
-      <x:c r="G7" s="73" t="str">
-        <x:v>Catering Cost</x:v>
-      </x:c>
-      <x:c r="H7" s="73" t="str">
-        <x:v>Staffing Cost</x:v>
-      </x:c>
-      <x:c r="I7" s="73" t="str">
-        <x:v>Net Profit</x:v>
-      </x:c>
-      <x:c r="J7" s="74" t="str">
-        <x:v>Status</x:v>
-      </x:c>
+      <x:c r="A7" s="242"/>
+      <x:c r="B7" s="243"/>
+      <x:c r="C7" s="243"/>
+      <x:c r="D7" s="243"/>
+      <x:c r="E7" s="243"/>
+      <x:c r="F7" s="243"/>
+      <x:c r="G7" s="243"/>
+      <x:c r="H7" s="243"/>
+      <x:c r="I7" s="243"/>
+      <x:c r="J7" s="244"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="60" t="str">
-        <x:v>AO-2601</x:v>
-      </x:c>
-      <x:c r="B8" s="61" t="str">
-        <x:v>Spring Gala</x:v>
-      </x:c>
-      <x:c r="C8" s="61" t="n">
-        <x:v>46096.5</x:v>
-      </x:c>
-      <x:c r="D8" s="61" t="str">
-        <x:v>Gala</x:v>
-      </x:c>
-      <x:c r="E8" s="61" t="n">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="F8" s="61" t="n">
-        <x:v>4800</x:v>
-      </x:c>
-      <x:c r="G8" s="61" t="n">
-        <x:v>1820</x:v>
-      </x:c>
-      <x:c r="H8" s="61" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I8" s="61" t="n">
-        <x:v>2980</x:v>
-      </x:c>
-      <x:c r="J8" s="62" t="str">
-        <x:v>Confirmed</x:v>
-      </x:c>
+      <x:c r="A8" s="245"/>
+      <x:c r="B8" s="246"/>
+      <x:c r="C8" s="246"/>
+      <x:c r="D8" s="246"/>
+      <x:c r="E8" s="246"/>
+      <x:c r="F8" s="246"/>
+      <x:c r="G8" s="246"/>
+      <x:c r="H8" s="246"/>
+      <x:c r="I8" s="246"/>
+      <x:c r="J8" s="247"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="60" t="str">
-        <x:v>AO-2602</x:v>
-      </x:c>
-      <x:c r="B9" s="61" t="str">
-        <x:v>Corporate Retreat</x:v>
-      </x:c>
-      <x:c r="C9" s="61" t="n">
-        <x:v>46150.5</x:v>
-      </x:c>
-      <x:c r="D9" s="61" t="str">
-        <x:v>Retreat</x:v>
-      </x:c>
-      <x:c r="E9" s="61" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F9" s="61" t="n">
-        <x:v>3200</x:v>
-      </x:c>
-      <x:c r="G9" s="61" t="n">
-        <x:v>1210</x:v>
-      </x:c>
-      <x:c r="H9" s="61" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I9" s="61" t="n">
-        <x:v>1990</x:v>
-      </x:c>
-      <x:c r="J9" s="62" t="str">
-        <x:v>Confirmed</x:v>
-      </x:c>
+      <x:c r="A9" s="245"/>
+      <x:c r="B9" s="246"/>
+      <x:c r="C9" s="246"/>
+      <x:c r="D9" s="246"/>
+      <x:c r="E9" s="246"/>
+      <x:c r="F9" s="246"/>
+      <x:c r="G9" s="246"/>
+      <x:c r="H9" s="246"/>
+      <x:c r="I9" s="246"/>
+      <x:c r="J9" s="247"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="60" t="str">
-        <x:v>AO-2603</x:v>
-      </x:c>
-      <x:c r="B10" s="61" t="str">
-        <x:v>Summer Wedding</x:v>
-      </x:c>
-      <x:c r="C10" s="61" t="n">
-        <x:v>46194.5</x:v>
-      </x:c>
-      <x:c r="D10" s="61" t="str">
-        <x:v>Wedding</x:v>
-      </x:c>
-      <x:c r="E10" s="61" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="F10" s="61" t="n">
-        <x:v>9500</x:v>
-      </x:c>
-      <x:c r="G10" s="61" t="n">
-        <x:v>3100</x:v>
-      </x:c>
-      <x:c r="H10" s="61" t="n">
-        <x:v>890</x:v>
-      </x:c>
-      <x:c r="I10" s="61" t="n">
-        <x:v>5510</x:v>
-      </x:c>
-      <x:c r="J10" s="62" t="str">
-        <x:v>Confirmed</x:v>
-      </x:c>
+      <x:c r="A10" s="245"/>
+      <x:c r="B10" s="246"/>
+      <x:c r="C10" s="246"/>
+      <x:c r="D10" s="246"/>
+      <x:c r="E10" s="246"/>
+      <x:c r="F10" s="246"/>
+      <x:c r="G10" s="246"/>
+      <x:c r="H10" s="246"/>
+      <x:c r="I10" s="246"/>
+      <x:c r="J10" s="247"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="60" t="str">
-        <x:v>AO-2604</x:v>
-      </x:c>
-      <x:c r="B11" s="61" t="str">
-        <x:v>Fall Gala</x:v>
-      </x:c>
-      <x:c r="C11" s="61" t="n">
-        <x:v>46299.5</x:v>
-      </x:c>
-      <x:c r="D11" s="61" t="str">
-        <x:v>Gala</x:v>
-      </x:c>
-      <x:c r="E11" s="61" t="n">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F11" s="61" t="n">
-        <x:v>5200</x:v>
-      </x:c>
-      <x:c r="G11" s="61" t="n">
-        <x:v>1400</x:v>
-      </x:c>
-      <x:c r="H11" s="61" t="n">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="I11" s="61" t="n">
-        <x:v>3290</x:v>
-      </x:c>
-      <x:c r="J11" s="62" t="str">
-        <x:v>Tentative</x:v>
-      </x:c>
+      <x:c r="A11" s="245"/>
+      <x:c r="B11" s="246"/>
+      <x:c r="C11" s="246"/>
+      <x:c r="D11" s="246"/>
+      <x:c r="E11" s="246"/>
+      <x:c r="F11" s="246"/>
+      <x:c r="G11" s="246"/>
+      <x:c r="H11" s="246"/>
+      <x:c r="I11" s="246"/>
+      <x:c r="J11" s="247"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="60" t="str">
-        <x:v>AO-2605</x:v>
-      </x:c>
-      <x:c r="B12" s="61" t="str">
-        <x:v>Winter Fundraiser</x:v>
-      </x:c>
-      <x:c r="C12" s="61" t="n">
-        <x:v>46368.5</x:v>
-      </x:c>
-      <x:c r="D12" s="61" t="str">
-        <x:v>Fundraiser</x:v>
-      </x:c>
-      <x:c r="E12" s="61" t="n">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="F12" s="61" t="n">
-        <x:v>7400</x:v>
-      </x:c>
-      <x:c r="G12" s="61" t="n">
-        <x:v>2625</x:v>
-      </x:c>
-      <x:c r="H12" s="61" t="n">
-        <x:v>670</x:v>
-      </x:c>
-      <x:c r="I12" s="61" t="n">
-        <x:v>4105</x:v>
-      </x:c>
-      <x:c r="J12" s="62" t="str">
-        <x:v>Tentative</x:v>
-      </x:c>
+      <x:c r="A12" s="245"/>
+      <x:c r="B12" s="246"/>
+      <x:c r="C12" s="246"/>
+      <x:c r="D12" s="246"/>
+      <x:c r="E12" s="246"/>
+      <x:c r="F12" s="246"/>
+      <x:c r="G12" s="246"/>
+      <x:c r="H12" s="246"/>
+      <x:c r="I12" s="246"/>
+      <x:c r="J12" s="247"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="60" t="str">
-        <x:v>AO-2606</x:v>
-      </x:c>
-      <x:c r="B13" s="61" t="str">
-        <x:v>Board Appreciation Dinner</x:v>
-      </x:c>
-      <x:c r="C13" s="61" t="n">
-        <x:v>46073.5</x:v>
-      </x:c>
-      <x:c r="D13" s="61" t="str">
-        <x:v>Dinner</x:v>
-      </x:c>
-      <x:c r="E13" s="61" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F13" s="61" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="G13" s="61" t="n">
-        <x:v>960</x:v>
-      </x:c>
-      <x:c r="H13" s="61" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="I13" s="61" t="n">
-        <x:v>1350</x:v>
-      </x:c>
-      <x:c r="J13" s="62" t="str">
-        <x:v>Completed</x:v>
-      </x:c>
+      <x:c r="A13" s="245"/>
+      <x:c r="B13" s="246"/>
+      <x:c r="C13" s="246"/>
+      <x:c r="D13" s="246"/>
+      <x:c r="E13" s="246"/>
+      <x:c r="F13" s="246"/>
+      <x:c r="G13" s="246"/>
+      <x:c r="H13" s="246"/>
+      <x:c r="I13" s="246"/>
+      <x:c r="J13" s="247"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="60" t="str">
-        <x:v>AO-2607</x:v>
-      </x:c>
-      <x:c r="B14" s="61" t="str">
-        <x:v>Community Awards Brunch</x:v>
-      </x:c>
-      <x:c r="C14" s="61" t="n">
-        <x:v>46250.5</x:v>
-      </x:c>
-      <x:c r="D14" s="61" t="str">
-        <x:v>Brunch</x:v>
-      </x:c>
-      <x:c r="E14" s="61" t="n">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F14" s="61" t="n">
-        <x:v>4100</x:v>
-      </x:c>
-      <x:c r="G14" s="61" t="n">
-        <x:v>1505</x:v>
-      </x:c>
-      <x:c r="H14" s="61" t="n">
-        <x:v>380</x:v>
-      </x:c>
-      <x:c r="I14" s="61" t="n">
-        <x:v>2215</x:v>
-      </x:c>
-      <x:c r="J14" s="62" t="str">
-        <x:v>Confirmed</x:v>
-      </x:c>
+      <x:c r="A14" s="245"/>
+      <x:c r="B14" s="246"/>
+      <x:c r="C14" s="246"/>
+      <x:c r="D14" s="246"/>
+      <x:c r="E14" s="246"/>
+      <x:c r="F14" s="246"/>
+      <x:c r="G14" s="246"/>
+      <x:c r="H14" s="246"/>
+      <x:c r="I14" s="246"/>
+      <x:c r="J14" s="247"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="60" t="str">
-        <x:v>AO-2608</x:v>
-      </x:c>
-      <x:c r="B15" s="61" t="str">
-        <x:v>New Year Kickoff</x:v>
-      </x:c>
-      <x:c r="C15" s="61" t="n">
-        <x:v>46032.5</x:v>
-      </x:c>
-      <x:c r="D15" s="61" t="str">
-        <x:v>Reception</x:v>
-      </x:c>
-      <x:c r="E15" s="61" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F15" s="61" t="n">
-        <x:v>3900</x:v>
-      </x:c>
-      <x:c r="G15" s="61" t="n">
-        <x:v>1350</x:v>
-      </x:c>
-      <x:c r="H15" s="61" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="I15" s="61" t="n">
-        <x:v>2190</x:v>
-      </x:c>
-      <x:c r="J15" s="62" t="str">
-        <x:v>Completed</x:v>
-      </x:c>
+      <x:c r="A15" s="245"/>
+      <x:c r="B15" s="246"/>
+      <x:c r="C15" s="246"/>
+      <x:c r="D15" s="246"/>
+      <x:c r="E15" s="246"/>
+      <x:c r="F15" s="246"/>
+      <x:c r="G15" s="246"/>
+      <x:c r="H15" s="246"/>
+      <x:c r="I15" s="246"/>
+      <x:c r="J15" s="247"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="60" t="str">
-        <x:v>AO-2609</x:v>
-      </x:c>
-      <x:c r="B16" s="61" t="str">
-        <x:v>Leadership Breakfast</x:v>
-      </x:c>
-      <x:c r="C16" s="61" t="n">
-        <x:v>46045.5</x:v>
-      </x:c>
-      <x:c r="D16" s="61" t="str">
-        <x:v>Breakfast</x:v>
-      </x:c>
-      <x:c r="E16" s="61" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F16" s="61" t="n">
-        <x:v>2800</x:v>
-      </x:c>
-      <x:c r="G16" s="61" t="n">
-        <x:v>910</x:v>
-      </x:c>
-      <x:c r="H16" s="61" t="n">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="I16" s="61" t="n">
-        <x:v>1670</x:v>
-      </x:c>
-      <x:c r="J16" s="62" t="str">
-        <x:v>Completed</x:v>
-      </x:c>
+      <x:c r="A16" s="245"/>
+      <x:c r="B16" s="246"/>
+      <x:c r="C16" s="246"/>
+      <x:c r="D16" s="246"/>
+      <x:c r="E16" s="246"/>
+      <x:c r="F16" s="246"/>
+      <x:c r="G16" s="246"/>
+      <x:c r="H16" s="246"/>
+      <x:c r="I16" s="246"/>
+      <x:c r="J16" s="247"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="60" t="str">
-        <x:v>AO-2610</x:v>
-      </x:c>
-      <x:c r="B17" s="61" t="str">
-        <x:v>Client Workshop</x:v>
-      </x:c>
-      <x:c r="C17" s="61" t="n">
-        <x:v>46058.5</x:v>
-      </x:c>
-      <x:c r="D17" s="61" t="str">
-        <x:v>Workshop</x:v>
-      </x:c>
-      <x:c r="E17" s="61" t="n">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F17" s="61" t="n">
-        <x:v>2400</x:v>
-      </x:c>
-      <x:c r="G17" s="61" t="n">
-        <x:v>780</x:v>
-      </x:c>
-      <x:c r="H17" s="61" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="I17" s="61" t="n">
-        <x:v>1440</x:v>
-      </x:c>
-      <x:c r="J17" s="62" t="str">
-        <x:v>Completed</x:v>
-      </x:c>
+      <x:c r="A17" s="245"/>
+      <x:c r="B17" s="246"/>
+      <x:c r="C17" s="246"/>
+      <x:c r="D17" s="246"/>
+      <x:c r="E17" s="246"/>
+      <x:c r="F17" s="246"/>
+      <x:c r="G17" s="246"/>
+      <x:c r="H17" s="246"/>
+      <x:c r="I17" s="246"/>
+      <x:c r="J17" s="247"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="60" t="str">
-        <x:v>AO-2611</x:v>
-      </x:c>
-      <x:c r="B18" s="61" t="str">
-        <x:v>Product Launch</x:v>
-      </x:c>
-      <x:c r="C18" s="61" t="n">
-        <x:v>46084.5</x:v>
-      </x:c>
-      <x:c r="D18" s="61" t="str">
-        <x:v>Launch</x:v>
-      </x:c>
-      <x:c r="E18" s="61" t="n">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="F18" s="61" t="n">
-        <x:v>6800</x:v>
-      </x:c>
-      <x:c r="G18" s="61" t="n">
-        <x:v>2100</x:v>
-      </x:c>
-      <x:c r="H18" s="61" t="n">
-        <x:v>620</x:v>
-      </x:c>
-      <x:c r="I18" s="61" t="n">
-        <x:v>4080</x:v>
-      </x:c>
-      <x:c r="J18" s="62" t="str">
-        <x:v>Completed</x:v>
-      </x:c>
+      <x:c r="A18" s="245"/>
+      <x:c r="B18" s="246"/>
+      <x:c r="C18" s="246"/>
+      <x:c r="D18" s="246"/>
+      <x:c r="E18" s="246"/>
+      <x:c r="F18" s="246"/>
+      <x:c r="G18" s="246"/>
+      <x:c r="H18" s="246"/>
+      <x:c r="I18" s="246"/>
+      <x:c r="J18" s="247"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="60" t="str">
-        <x:v>AO-2612</x:v>
-      </x:c>
-      <x:c r="B19" s="61" t="str">
-        <x:v>Alumni Mixer</x:v>
-      </x:c>
-      <x:c r="C19" s="61" t="n">
-        <x:v>46109.5</x:v>
-      </x:c>
-      <x:c r="D19" s="61" t="str">
-        <x:v>Reception</x:v>
-      </x:c>
-      <x:c r="E19" s="61" t="n">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="F19" s="61" t="n">
-        <x:v>5100</x:v>
-      </x:c>
-      <x:c r="G19" s="61" t="n">
-        <x:v>1620</x:v>
-      </x:c>
-      <x:c r="H19" s="61" t="n">
-        <x:v>430</x:v>
-      </x:c>
-      <x:c r="I19" s="61" t="n">
-        <x:v>3050</x:v>
-      </x:c>
-      <x:c r="J19" s="62" t="str">
-        <x:v>Completed</x:v>
-      </x:c>
+      <x:c r="A19" s="245"/>
+      <x:c r="B19" s="246"/>
+      <x:c r="C19" s="246"/>
+      <x:c r="D19" s="246"/>
+      <x:c r="E19" s="246"/>
+      <x:c r="F19" s="246"/>
+      <x:c r="G19" s="246"/>
+      <x:c r="H19" s="246"/>
+      <x:c r="I19" s="246"/>
+      <x:c r="J19" s="247"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="60" t="str">
-        <x:v>AO-2613</x:v>
-      </x:c>
-      <x:c r="B20" s="61" t="str">
-        <x:v>Volunteer Luncheon</x:v>
-      </x:c>
-      <x:c r="C20" s="61" t="n">
-        <x:v>46123.5</x:v>
-      </x:c>
-      <x:c r="D20" s="61" t="str">
-        <x:v>Luncheon</x:v>
-      </x:c>
-      <x:c r="E20" s="61" t="n">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F20" s="61" t="n">
-        <x:v>3300</x:v>
-      </x:c>
-      <x:c r="G20" s="61" t="n">
-        <x:v>1150</x:v>
-      </x:c>
-      <x:c r="H20" s="61" t="n">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="I20" s="61" t="n">
-        <x:v>1890</x:v>
-      </x:c>
-      <x:c r="J20" s="62" t="str">
-        <x:v>Completed</x:v>
-      </x:c>
+      <x:c r="A20" s="245"/>
+      <x:c r="B20" s="246"/>
+      <x:c r="C20" s="246"/>
+      <x:c r="D20" s="246"/>
+      <x:c r="E20" s="246"/>
+      <x:c r="F20" s="246"/>
+      <x:c r="G20" s="246"/>
+      <x:c r="H20" s="246"/>
+      <x:c r="I20" s="246"/>
+      <x:c r="J20" s="247"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="60" t="str">
-        <x:v>AO-2614</x:v>
-      </x:c>
-      <x:c r="B21" s="61" t="str">
-        <x:v>Charity Auction</x:v>
-      </x:c>
-      <x:c r="C21" s="61" t="n">
-        <x:v>46136.5</x:v>
-      </x:c>
-      <x:c r="D21" s="61" t="str">
-        <x:v>Fundraiser</x:v>
-      </x:c>
-      <x:c r="E21" s="61" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="F21" s="61" t="n">
-        <x:v>8800</x:v>
-      </x:c>
-      <x:c r="G21" s="61" t="n">
-        <x:v>2950</x:v>
-      </x:c>
-      <x:c r="H21" s="61" t="n">
-        <x:v>760</x:v>
-      </x:c>
-      <x:c r="I21" s="61" t="n">
-        <x:v>5090</x:v>
-      </x:c>
-      <x:c r="J21" s="62" t="str">
-        <x:v>Completed</x:v>
-      </x:c>
+      <x:c r="A21" s="245"/>
+      <x:c r="B21" s="246"/>
+      <x:c r="C21" s="246"/>
+      <x:c r="D21" s="246"/>
+      <x:c r="E21" s="246"/>
+      <x:c r="F21" s="246"/>
+      <x:c r="G21" s="246"/>
+      <x:c r="H21" s="246"/>
+      <x:c r="I21" s="246"/>
+      <x:c r="J21" s="247"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="60" t="str">
-        <x:v>AO-2615</x:v>
-      </x:c>
-      <x:c r="B22" s="61" t="str">
-        <x:v>Strategy Offsite</x:v>
-      </x:c>
-      <x:c r="C22" s="61" t="n">
-        <x:v>46158.5</x:v>
-      </x:c>
-      <x:c r="D22" s="61" t="str">
-        <x:v>Retreat</x:v>
-      </x:c>
-      <x:c r="E22" s="61" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F22" s="61" t="n">
-        <x:v>2200</x:v>
-      </x:c>
-      <x:c r="G22" s="61" t="n">
-        <x:v>720</x:v>
-      </x:c>
-      <x:c r="H22" s="61" t="n">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="I22" s="61" t="n">
-        <x:v>1290</x:v>
-      </x:c>
-      <x:c r="J22" s="62" t="str">
-        <x:v>Completed</x:v>
-      </x:c>
+      <x:c r="A22" s="245"/>
+      <x:c r="B22" s="246"/>
+      <x:c r="C22" s="246"/>
+      <x:c r="D22" s="246"/>
+      <x:c r="E22" s="246"/>
+      <x:c r="F22" s="246"/>
+      <x:c r="G22" s="246"/>
+      <x:c r="H22" s="246"/>
+      <x:c r="I22" s="246"/>
+      <x:c r="J22" s="247"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="60" t="str">
-        <x:v>AO-2616</x:v>
-      </x:c>
-      <x:c r="B23" s="61" t="str">
-        <x:v>Graduation Reception</x:v>
-      </x:c>
-      <x:c r="C23" s="61" t="n">
-        <x:v>46179.5</x:v>
-      </x:c>
-      <x:c r="D23" s="61" t="str">
-        <x:v>Reception</x:v>
-      </x:c>
-      <x:c r="E23" s="61" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F23" s="61" t="n">
-        <x:v>7600</x:v>
-      </x:c>
-      <x:c r="G23" s="61" t="n">
-        <x:v>2480</x:v>
-      </x:c>
-      <x:c r="H23" s="61" t="n">
-        <x:v>690</x:v>
-      </x:c>
-      <x:c r="I23" s="61" t="n">
-        <x:v>4430</x:v>
-      </x:c>
-      <x:c r="J23" s="62" t="str">
-        <x:v>Completed</x:v>
-      </x:c>
+      <x:c r="A23" s="245"/>
+      <x:c r="B23" s="246"/>
+      <x:c r="C23" s="246"/>
+      <x:c r="D23" s="246"/>
+      <x:c r="E23" s="246"/>
+      <x:c r="F23" s="246"/>
+      <x:c r="G23" s="246"/>
+      <x:c r="H23" s="246"/>
+      <x:c r="I23" s="246"/>
+      <x:c r="J23" s="247"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="60" t="str">
-        <x:v>AO-2617</x:v>
-      </x:c>
-      <x:c r="B24" s="61" t="str">
-        <x:v>Summer Picnic</x:v>
-      </x:c>
-      <x:c r="C24" s="61" t="n">
-        <x:v>46214.5</x:v>
-      </x:c>
-      <x:c r="D24" s="61" t="str">
-        <x:v>Picnic</x:v>
-      </x:c>
-      <x:c r="E24" s="61" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="F24" s="61" t="n">
-        <x:v>5800</x:v>
-      </x:c>
-      <x:c r="G24" s="61" t="n">
-        <x:v>2050</x:v>
-      </x:c>
-      <x:c r="H24" s="61" t="n">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="I24" s="61" t="n">
-        <x:v>3210</x:v>
-      </x:c>
-      <x:c r="J24" s="62" t="str">
-        <x:v>Confirmed</x:v>
-      </x:c>
+      <x:c r="A24" s="245"/>
+      <x:c r="B24" s="246"/>
+      <x:c r="C24" s="246"/>
+      <x:c r="D24" s="246"/>
+      <x:c r="E24" s="246"/>
+      <x:c r="F24" s="246"/>
+      <x:c r="G24" s="246"/>
+      <x:c r="H24" s="246"/>
+      <x:c r="I24" s="246"/>
+      <x:c r="J24" s="247"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="60" t="str">
-        <x:v>AO-2618</x:v>
-      </x:c>
-      <x:c r="B25" s="61" t="str">
-        <x:v>Donor Dinner</x:v>
-      </x:c>
-      <x:c r="C25" s="61" t="n">
-        <x:v>46228.5</x:v>
-      </x:c>
-      <x:c r="D25" s="61" t="str">
-        <x:v>Dinner</x:v>
-      </x:c>
-      <x:c r="E25" s="61" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F25" s="61" t="n">
-        <x:v>4700</x:v>
-      </x:c>
-      <x:c r="G25" s="61" t="n">
-        <x:v>1680</x:v>
-      </x:c>
-      <x:c r="H25" s="61" t="n">
-        <x:v>410</x:v>
-      </x:c>
-      <x:c r="I25" s="61" t="n">
-        <x:v>2610</x:v>
-      </x:c>
-      <x:c r="J25" s="62" t="str">
-        <x:v>Confirmed</x:v>
-      </x:c>
+      <x:c r="A25" s="245"/>
+      <x:c r="B25" s="246"/>
+      <x:c r="C25" s="246"/>
+      <x:c r="D25" s="246"/>
+      <x:c r="E25" s="246"/>
+      <x:c r="F25" s="246"/>
+      <x:c r="G25" s="246"/>
+      <x:c r="H25" s="246"/>
+      <x:c r="I25" s="246"/>
+      <x:c r="J25" s="247"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="60" t="str">
-        <x:v>AO-2619</x:v>
-      </x:c>
-      <x:c r="B26" s="61" t="str">
-        <x:v>Employee Recognition</x:v>
-      </x:c>
-      <x:c r="C26" s="61" t="n">
-        <x:v>46263.5</x:v>
-      </x:c>
-      <x:c r="D26" s="61" t="str">
-        <x:v>Reception</x:v>
-      </x:c>
-      <x:c r="E26" s="61" t="n">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="F26" s="61" t="n">
-        <x:v>4900</x:v>
-      </x:c>
-      <x:c r="G26" s="61" t="n">
-        <x:v>1710</x:v>
-      </x:c>
-      <x:c r="H26" s="61" t="n">
-        <x:v>460</x:v>
-      </x:c>
-      <x:c r="I26" s="61" t="n">
-        <x:v>2730</x:v>
-      </x:c>
-      <x:c r="J26" s="62" t="str">
-        <x:v>Confirmed</x:v>
-      </x:c>
+      <x:c r="A26" s="245"/>
+      <x:c r="B26" s="246"/>
+      <x:c r="C26" s="246"/>
+      <x:c r="D26" s="246"/>
+      <x:c r="E26" s="246"/>
+      <x:c r="F26" s="246"/>
+      <x:c r="G26" s="246"/>
+      <x:c r="H26" s="246"/>
+      <x:c r="I26" s="246"/>
+      <x:c r="J26" s="247"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="60" t="str">
-        <x:v>AO-2620</x:v>
-      </x:c>
-      <x:c r="B27" s="61" t="str">
-        <x:v>Networking Reception</x:v>
-      </x:c>
-      <x:c r="C27" s="61" t="n">
-        <x:v>46277.5</x:v>
-      </x:c>
-      <x:c r="D27" s="61" t="str">
-        <x:v>Reception</x:v>
-      </x:c>
-      <x:c r="E27" s="61" t="n">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="F27" s="61" t="n">
-        <x:v>6100</x:v>
-      </x:c>
-      <x:c r="G27" s="61" t="n">
-        <x:v>1975</x:v>
-      </x:c>
-      <x:c r="H27" s="61" t="n">
-        <x:v>580</x:v>
-      </x:c>
-      <x:c r="I27" s="61" t="n">
-        <x:v>3545</x:v>
-      </x:c>
-      <x:c r="J27" s="62" t="str">
-        <x:v>Confirmed</x:v>
-      </x:c>
+      <x:c r="A27" s="245"/>
+      <x:c r="B27" s="246"/>
+      <x:c r="C27" s="246"/>
+      <x:c r="D27" s="246"/>
+      <x:c r="E27" s="246"/>
+      <x:c r="F27" s="246"/>
+      <x:c r="G27" s="246"/>
+      <x:c r="H27" s="246"/>
+      <x:c r="I27" s="246"/>
+      <x:c r="J27" s="247"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="60" t="str">
-        <x:v>AO-2621</x:v>
-      </x:c>
-      <x:c r="B28" s="61" t="str">
-        <x:v>Annual Meeting</x:v>
-      </x:c>
-      <x:c r="C28" s="61" t="n">
-        <x:v>46291.5</x:v>
-      </x:c>
-      <x:c r="D28" s="61" t="str">
-        <x:v>Meeting</x:v>
-      </x:c>
-      <x:c r="E28" s="61" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F28" s="61" t="n">
-        <x:v>3500</x:v>
-      </x:c>
-      <x:c r="G28" s="61" t="n">
-        <x:v>1210</x:v>
-      </x:c>
-      <x:c r="H28" s="61" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="I28" s="61" t="n">
-        <x:v>1990</x:v>
-      </x:c>
-      <x:c r="J28" s="62" t="str">
-        <x:v>Confirmed</x:v>
-      </x:c>
+      <x:c r="A28" s="245"/>
+      <x:c r="B28" s="246"/>
+      <x:c r="C28" s="246"/>
+      <x:c r="D28" s="246"/>
+      <x:c r="E28" s="246"/>
+      <x:c r="F28" s="246"/>
+      <x:c r="G28" s="246"/>
+      <x:c r="H28" s="246"/>
+      <x:c r="I28" s="246"/>
+      <x:c r="J28" s="247"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="60" t="str">
-        <x:v>AO-2622</x:v>
-      </x:c>
-      <x:c r="B29" s="61" t="str">
-        <x:v>Holiday Market</x:v>
-      </x:c>
-      <x:c r="C29" s="61" t="n">
-        <x:v>46333.5</x:v>
-      </x:c>
-      <x:c r="D29" s="61" t="str">
-        <x:v>Market</x:v>
-      </x:c>
-      <x:c r="E29" s="61" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="F29" s="61" t="n">
-        <x:v>9800</x:v>
-      </x:c>
-      <x:c r="G29" s="61" t="n">
-        <x:v>3400</x:v>
-      </x:c>
-      <x:c r="H29" s="61" t="n">
-        <x:v>920</x:v>
-      </x:c>
-      <x:c r="I29" s="61" t="n">
-        <x:v>5480</x:v>
-      </x:c>
-      <x:c r="J29" s="62" t="str">
-        <x:v>Tentative</x:v>
-      </x:c>
+      <x:c r="A29" s="245"/>
+      <x:c r="B29" s="246"/>
+      <x:c r="C29" s="246"/>
+      <x:c r="D29" s="246"/>
+      <x:c r="E29" s="246"/>
+      <x:c r="F29" s="246"/>
+      <x:c r="G29" s="246"/>
+      <x:c r="H29" s="246"/>
+      <x:c r="I29" s="246"/>
+      <x:c r="J29" s="247"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="60" t="str">
-        <x:v>AO-2623</x:v>
-      </x:c>
-      <x:c r="B30" s="61" t="str">
-        <x:v>Team Celebration</x:v>
-      </x:c>
-      <x:c r="C30" s="61" t="n">
-        <x:v>46346.5</x:v>
-      </x:c>
-      <x:c r="D30" s="61" t="str">
-        <x:v>Dinner</x:v>
-      </x:c>
-      <x:c r="E30" s="61" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F30" s="61" t="n">
-        <x:v>3100</x:v>
-      </x:c>
-      <x:c r="G30" s="61" t="n">
-        <x:v>1050</x:v>
-      </x:c>
-      <x:c r="H30" s="61" t="n">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="I30" s="61" t="n">
-        <x:v>1800</x:v>
-      </x:c>
-      <x:c r="J30" s="62" t="str">
-        <x:v>Tentative</x:v>
-      </x:c>
+      <x:c r="A30" s="245"/>
+      <x:c r="B30" s="246"/>
+      <x:c r="C30" s="246"/>
+      <x:c r="D30" s="246"/>
+      <x:c r="E30" s="246"/>
+      <x:c r="F30" s="246"/>
+      <x:c r="G30" s="246"/>
+      <x:c r="H30" s="246"/>
+      <x:c r="I30" s="246"/>
+      <x:c r="J30" s="247"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="63" t="str">
-        <x:v>AO-2624</x:v>
-      </x:c>
-      <x:c r="B31" s="64" t="str">
-        <x:v>Year-End Dinner</x:v>
-      </x:c>
-      <x:c r="C31" s="64" t="n">
-        <x:v>46375.5</x:v>
-      </x:c>
-      <x:c r="D31" s="64" t="str">
-        <x:v>Dinner</x:v>
-      </x:c>
-      <x:c r="E31" s="64" t="n">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="F31" s="64" t="n">
-        <x:v>6900</x:v>
-      </x:c>
-      <x:c r="G31" s="64" t="n">
-        <x:v>2380</x:v>
-      </x:c>
-      <x:c r="H31" s="64" t="n">
-        <x:v>640</x:v>
-      </x:c>
-      <x:c r="I31" s="64" t="n">
-        <x:v>3880</x:v>
-      </x:c>
-      <x:c r="J31" s="65" t="str">
-        <x:v>Tentative</x:v>
-      </x:c>
+      <x:c r="A31" s="248"/>
+      <x:c r="B31" s="249"/>
+      <x:c r="C31" s="249"/>
+      <x:c r="D31" s="249"/>
+      <x:c r="E31" s="249"/>
+      <x:c r="F31" s="249"/>
+      <x:c r="G31" s="249"/>
+      <x:c r="H31" s="249"/>
+      <x:c r="I31" s="249"/>
+      <x:c r="J31" s="250"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3370,206 +3214,230 @@
       <x:c r="E2" s="97"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="111" t="str">
+      <x:c r="A4" s="251" t="str">
         <x:v>Step</x:v>
       </x:c>
-      <x:c r="B4" s="111" t="str">
+      <x:c r="B4" s="251" t="str">
         <x:v>Requirement</x:v>
       </x:c>
-      <x:c r="C4" s="111" t="str">
+      <x:c r="C4" s="251" t="str">
         <x:v>Where</x:v>
       </x:c>
-      <x:c r="D4" s="111" t="str">
+      <x:c r="D4" s="251" t="str">
         <x:v>When</x:v>
       </x:c>
-      <x:c r="E4" s="111" t="str">
+      <x:c r="E4" s="251" t="str">
         <x:v>Completion evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="52" customHeight="1">
-      <x:c r="A5" s="181" t="str">
+    <x:row r="5" ht="68" customHeight="1">
+      <x:c r="A5" s="262" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="101" t="str">
+      <x:c r="B5" s="259" t="str">
         <x:v>Preserve every Raw Export header and record exactly as provided.</x:v>
       </x:c>
-      <x:c r="C5" s="101" t="str">
+      <x:c r="C5" s="259" t="str">
         <x:v>Raw Export!A1:J25</x:v>
       </x:c>
-      <x:c r="D5" s="101" t="str">
+      <x:c r="D5" s="259" t="str">
         <x:v>Always</x:v>
       </x:c>
-      <x:c r="E5" s="101" t="str">
+      <x:c r="E5" s="259" t="str">
         <x:v>No values, rows, columns, or sheet names changed</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="52" customHeight="1">
-      <x:c r="A6" s="181" t="str">
+    <x:row r="6" ht="82" customHeight="1">
+      <x:c r="A6" s="262" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B6" s="101" t="str">
+      <x:c r="B6" s="259" t="str">
+        <x:v>Copy Raw Export!A1:J25, use Paste Values beginning at Manager View!A7, then replace the 10 snake_case headers with readable labels without changing any detail value.</x:v>
+      </x:c>
+      <x:c r="C6" s="259" t="str">
+        <x:v>Raw Export → Manager View!A7:J31</x:v>
+      </x:c>
+      <x:c r="D6" s="259" t="str">
+        <x:v>In class · first</x:v>
+      </x:c>
+      <x:c r="E6" s="259" t="str">
+        <x:v>All 24 records and 10 readable headers appear; Raw Export remains unchanged</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="68" customHeight="1">
+      <x:c r="A7" s="262" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B7" s="259" t="str">
         <x:v>Convert the full manager data range into one Excel table and keep filter buttons available.</x:v>
       </x:c>
-      <x:c r="C6" s="101" t="str">
+      <x:c r="C7" s="259" t="str">
         <x:v>Manager View!A7:J31</x:v>
       </x:c>
-      <x:c r="D6" s="101" t="str">
+      <x:c r="D7" s="259" t="str">
         <x:v>In class</x:v>
       </x:c>
-      <x:c r="E6" s="101" t="str">
+      <x:c r="E7" s="259" t="str">
         <x:v>All 24 records and headers are inside one table</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="52" customHeight="1">
-      <x:c r="A7" s="181" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B7" s="101" t="str">
+    <x:row r="8" ht="68" customHeight="1">
+      <x:c r="A8" s="262" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B8" s="259" t="str">
         <x:v>Use meaningful formats for the date, whole-number Guests, and business-money columns.</x:v>
       </x:c>
-      <x:c r="C7" s="101" t="str">
+      <x:c r="C8" s="259" t="str">
         <x:v>Manager View</x:v>
       </x:c>
-      <x:c r="D7" s="101" t="str">
+      <x:c r="D8" s="259" t="str">
         <x:v>In class</x:v>
       </x:c>
-      <x:c r="E7" s="101" t="str">
+      <x:c r="E8" s="259" t="str">
         <x:v>Every format communicates what its column means</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="52" customHeight="1">
-      <x:c r="A8" s="181" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B8" s="101" t="str">
+    <x:row r="9" ht="68" customHeight="1">
+      <x:c r="A9" s="262" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B9" s="259" t="str">
         <x:v>Set readable widths and alignment so long labels and values can be scanned without avoidable clipping.</x:v>
       </x:c>
-      <x:c r="C8" s="101" t="str">
+      <x:c r="C9" s="259" t="str">
         <x:v>Manager View!A:J</x:v>
       </x:c>
-      <x:c r="D8" s="101" t="str">
+      <x:c r="D9" s="259" t="str">
         <x:v>In class</x:v>
       </x:c>
-      <x:c r="E8" s="101" t="str">
+      <x:c r="E9" s="259" t="str">
         <x:v>Event names and headings are readable</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="52" customHeight="1">
-      <x:c r="A9" s="181" t="str">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B9" s="101" t="str">
+    <x:row r="10" ht="68" customHeight="1">
+      <x:c r="A10" s="262" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B10" s="259" t="str">
         <x:v>Select A8 and freeze the rows above it so the actual table header remains visible.</x:v>
       </x:c>
-      <x:c r="C9" s="101" t="str">
+      <x:c r="C10" s="259" t="str">
         <x:v>Manager View</x:v>
       </x:c>
-      <x:c r="D9" s="101" t="str">
+      <x:c r="D10" s="259" t="str">
         <x:v>In class</x:v>
       </x:c>
-      <x:c r="E9" s="101" t="str">
+      <x:c r="E10" s="259" t="str">
         <x:v>Row 7 remains visible while scrolling</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="52" customHeight="1">
-      <x:c r="A10" s="181" t="str">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B10" s="101" t="str">
+    <x:row r="11" ht="68" customHeight="1">
+      <x:c r="A11" s="262" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B11" s="259" t="str">
         <x:v>Build the four labeled summaries for Total Revenue, Total Net Profit, Average Revenue per Event, and Total Guests.</x:v>
       </x:c>
-      <x:c r="C10" s="101" t="str">
+      <x:c r="C11" s="259" t="str">
         <x:v>Manager View!C3, F3, I3, L3</x:v>
       </x:c>
-      <x:c r="D10" s="101" t="str">
+      <x:c r="D11" s="259" t="str">
         <x:v>After class</x:v>
       </x:c>
-      <x:c r="E10" s="101" t="str">
+      <x:c r="E11" s="259" t="str">
         <x:v>Each result is a formula using worksheet or table references</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="52" customHeight="1">
-      <x:c r="A11" s="181" t="str">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B11" s="101" t="str">
+    <x:row r="12" ht="68" customHeight="1">
+      <x:c r="A12" s="262" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B12" s="259" t="str">
         <x:v>Apply one conditional-formatting rule to Net Profit and be able to state its business purpose.</x:v>
       </x:c>
-      <x:c r="C11" s="101" t="str">
+      <x:c r="C12" s="259" t="str">
         <x:v>Manager View!I8:I31</x:v>
       </x:c>
-      <x:c r="D11" s="101" t="str">
+      <x:c r="D12" s="259" t="str">
         <x:v>After class</x:v>
       </x:c>
-      <x:c r="E11" s="101" t="str">
+      <x:c r="E12" s="259" t="str">
         <x:v>The rule helps identify a high, low, or risky result</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="52" customHeight="1">
-      <x:c r="A12" s="181" t="str">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B12" s="101" t="str">
+    <x:row r="13" ht="68" customHeight="1">
+      <x:c r="A13" s="262" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B13" s="259" t="str">
         <x:v>Create a clear visual hierarchy with readable summaries, a usable table, and purposeful emphasis.</x:v>
       </x:c>
-      <x:c r="C12" s="101" t="str">
+      <x:c r="C13" s="259" t="str">
         <x:v>Manager View</x:v>
       </x:c>
-      <x:c r="D12" s="101" t="str">
+      <x:c r="D13" s="259" t="str">
         <x:v>Final audit</x:v>
       </x:c>
-      <x:c r="E12" s="101" t="str">
+      <x:c r="E13" s="259" t="str">
         <x:v>A manager can understand the workbook in about 30 seconds</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="52" customHeight="1">
-      <x:c r="A13" s="181" t="str">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B13" s="101" t="str">
+    <x:row r="14" ht="68" customHeight="1">
+      <x:c r="A14" s="262" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B14" s="259" t="str">
         <x:v>Save and submit the original .xlsx with all required sheet names intact.</x:v>
       </x:c>
-      <x:c r="C13" s="101" t="str">
+      <x:c r="C14" s="259" t="str">
         <x:v>Whole workbook</x:v>
       </x:c>
-      <x:c r="D13" s="101" t="str">
+      <x:c r="D14" s="259" t="str">
         <x:v>Submit</x:v>
       </x:c>
-      <x:c r="E13" s="101" t="str">
+      <x:c r="E14" s="259" t="str">
         <x:v>Workbook opens normally; do not submit PDF or CSV</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="182" t="str">
+    <x:row r="15" ht="12" customHeight="1">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+    </x:row>
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16" s="268" t="str">
         <x:v>Timing</x:v>
       </x:c>
-      <x:c r="B15" s="182" t="str">
+      <x:c r="B16" s="268" t="str">
         <x:v>In class · about 25 minutes</x:v>
       </x:c>
-      <x:c r="C15" s="182" t="str">
+      <x:c r="C16" s="268" t="str">
         <x:v>After class · about 30–40 minutes</x:v>
       </x:c>
-      <x:c r="D15" s="182" t="str">
+      <x:c r="D16" s="268" t="str">
         <x:v>Grading</x:v>
       </x:c>
-      <x:c r="E15" s="182" t="str">
+      <x:c r="E16" s="268" t="str">
         <x:v>Submission</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="54" customHeight="1">
-      <x:c r="A16" s="101" t="str">
-        <x:v>Start the structure before you leave class.</x:v>
-      </x:c>
-      <x:c r="B16" s="101" t="str">
-        <x:v>Table, filters, widths, alignment, number formats, Freeze Panes</x:v>
-      </x:c>
-      <x:c r="C16" s="101" t="str">
+    <x:row r="17" ht="68" customHeight="1">
+      <x:c r="A17" s="270" t="str">
+        <x:v>Create the working copy before you format.</x:v>
+      </x:c>
+      <x:c r="B17" s="270" t="str">
+        <x:v>Paste values, rename headers, build the table, then add filters, widths, alignment, number formats, and Freeze Panes</x:v>
+      </x:c>
+      <x:c r="C17" s="270" t="str">
         <x:v>Four formulas, one purposeful rule, 30-second audit</x:v>
       </x:c>
-      <x:c r="D16" s="101" t="str">
+      <x:c r="D17" s="270" t="str">
         <x:v>27 automatic + 3 visual spot-check = 30 points</x:v>
       </x:c>
-      <x:c r="E16" s="101" t="str">
+      <x:c r="E17" s="270" t="str">
         <x:v>Upload the completed .xlsx; do not submit PDF or CSV</x:v>
       </x:c>
     </x:row>
@@ -3664,16 +3532,16 @@
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="101" t="str">
-        <x:v>Excel table</x:v>
+        <x:v>Working-copy table</x:v>
       </x:c>
       <x:c r="B6" s="189" t="str">
-        <x:v>Select the full range</x:v>
+        <x:v>Paste Values at A7, then select A7:J31</x:v>
       </x:c>
       <x:c r="C6" s="101" t="str">
-        <x:v>Adds structure, banding, and filters.</x:v>
+        <x:v>Creates a separate manager view before adding structure and filters.</x:v>
       </x:c>
       <x:c r="D6" s="190" t="str">
-        <x:v>Include every header and all 24 records.</x:v>
+        <x:v>Raw Export stays unchanged; include all 24 records.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="42" customHeight="1">

--- a/EXCEL/M02/bus123-excel-m02-l01-starter.xlsx
+++ b/EXCEL/M02/bus123-excel-m02-l01-starter.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Reb27bf64c1e84923"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="Rb9af3a372f924282"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Export" sheetId="3" r:id="R944fc666fb644469"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manager View" sheetId="4" r:id="Rb50bf440824249b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="5" r:id="R27ef597b93b84559"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="6" r:id="R91f20e56d7714e06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R68b84be923024d2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="Rb1c8ca2660f14d24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Export" sheetId="3" r:id="Ref2fb5b8544240bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manager View" sheetId="4" r:id="R9a90e5102b4f45db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="5" r:id="R8eff6ffd248f44c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="6" r:id="Re671bd319c664391"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,7 +22,7 @@
     <x:numFmt numFmtId="200" formatCode="$#,##0"/>
     <x:numFmt numFmtId="201" formatCode="General"/>
   </x:numFmts>
-  <x:fonts count="23">
+  <x:fonts count="24">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -155,8 +155,15 @@
       <x:color rgb="FF355773"/>
       <x:name val="Aptos"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF355773"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="22">
+  <x:fills count="23">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -263,8 +270,13 @@
         <x:fgColor rgb="FF4A7C5E"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="44">
+  <x:borders count="48">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -676,11 +688,55 @@
       </x:top>
       <x:bottom style="none"/>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF4A7C5E"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FF4A7C5E"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF4A7C5E"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FF4A7C5E"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF4A7C5E"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF4A7C5E"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF4A7C5E"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF4A7C5E"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color rgb="FF4A7C5E"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF4A7C5E"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF4A7C5E"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF4A7C5E"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="271">
+  <x:cellXfs count="290">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1269,6 +1325,47 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="22" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="22" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="22" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="22" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="22" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="22" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="22" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="22" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="22" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="22" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="22" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="22" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="22" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="22" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="22" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="22" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="22" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -2823,7 +2920,7 @@
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="97" t="str">
-        <x:v>Begin only when your instructor directs you. Copy Raw Export!A1:J25, paste values at A7, replace the snake_case headers with readable labels, then build the working table and summaries here.</x:v>
+        <x:v>Begin only when your instructor directs you. Copy Raw Export!A1:J25, paste values at A7, replace the snake_case headers with readable labels, then build the working table. The pale-green cells in C3, F3, I3, and L3 are formula results to complete after class.</x:v>
       </x:c>
       <x:c r="B2" s="97"/>
       <x:c r="C2" s="97"/>
@@ -2841,22 +2938,38 @@
       <x:c r="B3" s="53" t="str">
         <x:v>Total Revenue</x:v>
       </x:c>
-      <x:c r="C3" s="54"/>
+      <x:c r="C3" s="289"/>
       <x:c r="D3"/>
       <x:c r="E3" s="53" t="str">
         <x:v>Total Net Profit</x:v>
       </x:c>
-      <x:c r="F3" s="54"/>
+      <x:c r="F3" s="289"/>
       <x:c r="G3"/>
       <x:c r="H3" s="53" t="str">
         <x:v>Average Revenue / Event</x:v>
       </x:c>
-      <x:c r="I3" s="54"/>
+      <x:c r="I3" s="289"/>
       <x:c r="J3"/>
       <x:c r="K3" s="53" t="str">
         <x:v>Total Guests</x:v>
       </x:c>
-      <x:c r="L3" s="54"/>
+      <x:c r="L3" s="289"/>
+    </x:row>
+    <x:row r="4" ht="34" customHeight="1">
+      <x:c r="A4" s="282" t="str">
+        <x:v>AFTER CLASS · Build each summary with a worksheet or table reference, then reconcile it to the 24 detail records. A blank or error-free cell is not evidence of a working formula.</x:v>
+      </x:c>
+      <x:c r="B4" s="283"/>
+      <x:c r="C4" s="283"/>
+      <x:c r="D4" s="283"/>
+      <x:c r="E4" s="283"/>
+      <x:c r="F4" s="283"/>
+      <x:c r="G4" s="283"/>
+      <x:c r="H4" s="283"/>
+      <x:c r="I4" s="283"/>
+      <x:c r="J4" s="283"/>
+      <x:c r="K4" s="283"/>
+      <x:c r="L4" s="284"/>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
       <x:c r="A5" s="177" t="str">
@@ -3179,6 +3292,7 @@
     <x:mergeCell ref="A1:L1"/>
     <x:mergeCell ref="A2:L2"/>
     <x:mergeCell ref="A5:L5"/>
+    <x:mergeCell ref="A4:L4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
